--- a/docs/files-completion-list/ui-pages-trading-alerts-saas-public.xlsx
+++ b/docs/files-completion-list/ui-pages-trading-alerts-saas-public.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\docs\files-completion-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EB1BC6-A6C3-40B1-A8C1-F052092CF789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813AF325-EC05-4A71-959C-A348412F891E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="1" xr2:uid="{226B384D-6115-4E82-9FF4-20CA6CB65055}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{226B384D-6115-4E82-9FF4-20CA6CB65055}"/>
   </bookViews>
   <sheets>
     <sheet name="trading_alerts_saas_pages" sheetId="5" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="961">
   <si>
     <t xml:space="preserve"> Index </t>
   </si>
@@ -2656,12 +2656,6 @@
     <t>Here are pages that user could access if it logged in as Admin account (Excluding pages that are for tests or working in background)</t>
   </si>
   <si>
-    <t>Page Display without Login (Existing Status) [BEFORE]</t>
-  </si>
-  <si>
-    <t>Page Display without Login (Propose change) [AFTER]</t>
-  </si>
-  <si>
     <t>Page Display as FREE user Login (Existing Status) [BEFORE]</t>
   </si>
   <si>
@@ -2849,6 +2843,87 @@
   </si>
   <si>
     <t># Tier: FREE</t>
+  </si>
+  <si>
+    <t>Sign in page (working correctly)</t>
+  </si>
+  <si>
+    <t>Landing/welcome page (working correctly)</t>
+  </si>
+  <si>
+    <t>About Trading Alerts (working correctly)</t>
+  </si>
+  <si>
+    <t>Page not found (404) (working correctly)</t>
+  </si>
+  <si>
+    <t>Become an Affiliate (working correctly)</t>
+  </si>
+  <si>
+    <t>Affiliate Marking Resources (working correctly)</t>
+  </si>
+  <si>
+    <t>Page not found (404) | (working incorrectly by not redirect to sign in page)</t>
+  </si>
+  <si>
+    <t>Become a Trading Alerts Affiliate (working correctly)</t>
+  </si>
+  <si>
+    <t>Blog (working correctly)</t>
+  </si>
+  <si>
+    <t>Careers (working correctly)</t>
+  </si>
+  <si>
+    <t>Changelog | (working incorrectly by not redirect to sign in page)</t>
+  </si>
+  <si>
+    <t>Verify Your Email | (working incorrectly by not redirect to sign in page)</t>
+  </si>
+  <si>
+    <t>Unable to show payment status | (working incorrectly by not redirect to sign page)</t>
+  </si>
+  <si>
+    <t>Financial Risk Disclaimer (working correctly)</t>
+  </si>
+  <si>
+    <t>Documentation (working correctly)</t>
+  </si>
+  <si>
+    <t>Forgot Password? (working correctly)</t>
+  </si>
+  <si>
+    <t>Help Center (working correctly)</t>
+  </si>
+  <si>
+    <t>Choose Your Plan (working correctly)</t>
+  </si>
+  <si>
+    <t>Privacy Policy (working correctly)</t>
+  </si>
+  <si>
+    <t>Create Your Account (working correctly)</t>
+  </si>
+  <si>
+    <t>Invalid link / Request a new link (working correctly)</t>
+  </si>
+  <si>
+    <t>System Status | (working incorrectly by not redirect to sign page)</t>
+  </si>
+  <si>
+    <t>Terms of Service (working correctly)</t>
+  </si>
+  <si>
+    <t>No active 2FA verification challenge found (working correctly)</t>
+  </si>
+  <si>
+    <t>Check your email (working correctly)</t>
+  </si>
+  <si>
+    <t>Verification link missing (working correctly)</t>
+  </si>
+  <si>
+    <t>Page Display without Login [TEST RESULT]</t>
   </si>
 </sst>
 </file>
@@ -3032,11 +3107,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3402,98 +3476,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21EDD11-0712-4E9B-9D43-4012822F0DE1}">
-  <dimension ref="A1:U93"/>
+  <dimension ref="A1:T93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="7.3125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.62890625" customWidth="1"/>
     <col min="4" max="4" width="38.7890625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="76.734375" customWidth="1"/>
-    <col min="6" max="6" width="48.41796875" customWidth="1"/>
-    <col min="7" max="7" width="18.47265625" customWidth="1"/>
-    <col min="8" max="8" width="15.05078125" customWidth="1"/>
-    <col min="9" max="9" width="80.734375" customWidth="1"/>
-    <col min="10" max="10" width="82" customWidth="1"/>
-    <col min="11" max="11" width="16.734375" customWidth="1"/>
-    <col min="12" max="12" width="27.3125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.62890625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.3125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.41796875" customWidth="1"/>
-    <col min="16" max="16" width="27.3125" customWidth="1"/>
-    <col min="17" max="17" width="31.41796875" customWidth="1"/>
-    <col min="18" max="18" width="29.83984375" customWidth="1"/>
-    <col min="19" max="19" width="29.3125" customWidth="1"/>
-    <col min="20" max="20" width="34.26171875" customWidth="1"/>
-    <col min="21" max="21" width="30.7890625" customWidth="1"/>
-    <col min="22" max="24" width="8.83984375" customWidth="1"/>
+    <col min="5" max="5" width="23.05078125" customWidth="1"/>
+    <col min="6" max="6" width="48.41796875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18.47265625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="15.05078125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="80.734375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="82" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="13.83984375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="77.9453125" customWidth="1"/>
+    <col min="13" max="13" width="27.3125" customWidth="1"/>
+    <col min="14" max="14" width="30.41796875" customWidth="1"/>
+    <col min="15" max="15" width="27.3125" customWidth="1"/>
+    <col min="16" max="16" width="31.41796875" customWidth="1"/>
+    <col min="17" max="17" width="29.83984375" customWidth="1"/>
+    <col min="18" max="18" width="29.3125" customWidth="1"/>
+    <col min="19" max="19" width="34.26171875" customWidth="1"/>
+    <col min="20" max="20" width="30.7890625" customWidth="1"/>
+    <col min="21" max="23" width="8.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:20" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>871</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>872</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>873</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>874</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
         <v>875</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>876</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="6" t="s">
         <v>877</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="T1" s="6" t="s">
         <v>878</v>
       </c>
-      <c r="T1" s="7" t="s">
-        <v>879</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3528,37 +3598,34 @@
         <v>179</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="M2" s="15" t="s">
         <v>772</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="15" t="s">
         <v>772</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="O2" s="21" t="s">
         <v>772</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="P2" s="21" t="s">
         <v>772</v>
       </c>
-      <c r="P2" s="22" t="s">
+      <c r="Q2" s="27" t="s">
         <v>772</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="R2" s="27" t="s">
         <v>772</v>
       </c>
-      <c r="R2" s="28" t="s">
+      <c r="S2" s="33" t="s">
         <v>772</v>
       </c>
-      <c r="S2" s="28" t="s">
+      <c r="T2" s="33" t="s">
         <v>772</v>
       </c>
-      <c r="T2" s="34" t="s">
-        <v>772</v>
-      </c>
-      <c r="U2" s="34" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>525</v>
       </c>
@@ -3593,37 +3660,34 @@
         <v>179</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="M3" s="15" t="s">
         <v>789</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="15" t="s">
         <v>789</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="O3" s="21" t="s">
         <v>789</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="P3" s="21" t="s">
         <v>789</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="Q3" s="27" t="s">
         <v>789</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="R3" s="27" t="s">
         <v>789</v>
       </c>
-      <c r="R3" s="28" t="s">
+      <c r="S3" s="33" t="s">
         <v>789</v>
       </c>
-      <c r="S3" s="28" t="s">
+      <c r="T3" s="33" t="s">
         <v>789</v>
       </c>
-      <c r="T3" s="34" t="s">
-        <v>789</v>
-      </c>
-      <c r="U3" s="34" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>458</v>
       </c>
@@ -3658,37 +3722,34 @@
         <v>179</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N4" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="O4" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P4" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q4" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R4" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="S4" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T4" s="34" t="s">
-        <v>732</v>
-      </c>
-      <c r="U4" s="34" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>937</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O4" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="P4" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q4" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="R4" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="T4" s="33" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>451</v>
       </c>
@@ -3723,37 +3784,34 @@
         <v>179</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N5" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P5" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q5" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R5" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="S5" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T5" s="34" t="s">
-        <v>732</v>
-      </c>
-      <c r="U5" s="34" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>937</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O5" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="P5" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q5" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="R5" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S5" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="T5" s="33" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>415</v>
       </c>
@@ -3787,38 +3845,35 @@
       <c r="K6" t="s">
         <v>179</v>
       </c>
-      <c r="L6" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N6" s="19" t="s">
+      <c r="L6" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M6" s="18" t="s">
         <v>773</v>
       </c>
-      <c r="O6" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P6" s="25" t="s">
+      <c r="N6" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O6" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q6" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R6" s="31" t="s">
+      <c r="P6" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q6" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T6" s="35" t="s">
+      <c r="R6" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S6" s="34" t="s">
         <v>813</v>
       </c>
-      <c r="U6" s="35" t="s">
+      <c r="T6" s="34" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>485</v>
       </c>
@@ -3852,38 +3907,35 @@
       <c r="K7" t="s">
         <v>179</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N7" s="19" t="s">
+      <c r="L7" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M7" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O7" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P7" s="25" t="s">
+      <c r="N7" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O7" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q7" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R7" s="31" t="s">
+      <c r="P7" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q7" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S7" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T7" s="36" t="s">
+      <c r="R7" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S7" s="35" t="s">
         <v>850</v>
       </c>
-      <c r="U7" s="40" t="s">
+      <c r="T7" s="39" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -3917,38 +3969,35 @@
       <c r="K8" t="s">
         <v>179</v>
       </c>
-      <c r="L8" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N8" s="19" t="s">
+      <c r="L8" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M8" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O8" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P8" s="25" t="s">
+      <c r="N8" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O8" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q8" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R8" s="31" t="s">
+      <c r="P8" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q8" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S8" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T8" s="35" t="s">
+      <c r="R8" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S8" s="34" t="s">
         <v>814</v>
       </c>
-      <c r="U8" s="35" t="s">
+      <c r="T8" s="34" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -3982,38 +4031,35 @@
       <c r="K9" t="s">
         <v>179</v>
       </c>
-      <c r="L9" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N9" s="19" t="s">
+      <c r="L9" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M9" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O9" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P9" s="25" t="s">
+      <c r="N9" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O9" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q9" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R9" s="31" t="s">
+      <c r="P9" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S9" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T9" s="35" t="s">
+      <c r="R9" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S9" s="34" t="s">
         <v>815</v>
       </c>
-      <c r="U9" s="35" t="s">
+      <c r="T9" s="34" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -4047,38 +4093,35 @@
       <c r="K10" t="s">
         <v>179</v>
       </c>
-      <c r="L10" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N10" s="19" t="s">
+      <c r="L10" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M10" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O10" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P10" s="25" t="s">
+      <c r="N10" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O10" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q10" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R10" s="31" t="s">
+      <c r="P10" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q10" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S10" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T10" s="35" t="s">
+      <c r="R10" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S10" s="34" t="s">
         <v>816</v>
       </c>
-      <c r="U10" s="35" t="s">
+      <c r="T10" s="34" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -4112,38 +4155,35 @@
       <c r="K11" t="s">
         <v>179</v>
       </c>
-      <c r="L11" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N11" s="19" t="s">
+      <c r="L11" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M11" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O11" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P11" s="25" t="s">
+      <c r="N11" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O11" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q11" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R11" s="31" t="s">
+      <c r="P11" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q11" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S11" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T11" s="35" t="s">
+      <c r="R11" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S11" s="34" t="s">
         <v>817</v>
       </c>
-      <c r="U11" s="35" t="s">
+      <c r="T11" s="34" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -4177,38 +4217,35 @@
       <c r="K12" t="s">
         <v>179</v>
       </c>
-      <c r="L12" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N12" s="19" t="s">
+      <c r="L12" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M12" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O12" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P12" s="25" t="s">
+      <c r="N12" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O12" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q12" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R12" s="31" t="s">
+      <c r="P12" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q12" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S12" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T12" s="35" t="s">
+      <c r="R12" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S12" s="34" t="s">
         <v>818</v>
       </c>
-      <c r="U12" s="35" t="s">
+      <c r="T12" s="34" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>58</v>
       </c>
@@ -4242,103 +4279,97 @@
       <c r="K13" t="s">
         <v>179</v>
       </c>
-      <c r="L13" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N13" s="19" t="s">
+      <c r="L13" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M13" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O13" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P13" s="25" t="s">
+      <c r="N13" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O13" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q13" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R13" s="31" t="s">
+      <c r="P13" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q13" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S13" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T13" s="35" t="s">
+      <c r="R13" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S13" s="34" t="s">
         <v>819</v>
       </c>
-      <c r="U13" s="35" t="s">
+      <c r="T13" s="34" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="L14" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N14" s="19" t="s">
+      <c r="L14" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M14" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O14" s="17" t="s">
-        <v>732</v>
-      </c>
-      <c r="P14" s="25" t="s">
+      <c r="N14" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="O14" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q14" s="23" t="s">
-        <v>732</v>
-      </c>
-      <c r="R14" s="31" t="s">
+      <c r="P14" s="22" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q14" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S14" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T14" s="35" t="s">
+      <c r="R14" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S14" s="34" t="s">
         <v>820</v>
       </c>
-      <c r="U14" s="35" t="s">
+      <c r="T14" s="34" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>499</v>
       </c>
@@ -4372,38 +4403,35 @@
       <c r="K15" t="s">
         <v>179</v>
       </c>
-      <c r="L15" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N15" s="19" t="s">
+      <c r="L15" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M15" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O15" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P15" s="25" t="s">
+      <c r="N15" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O15" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q15" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R15" s="31" t="s">
+      <c r="P15" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q15" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S15" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T15" s="35" t="s">
+      <c r="R15" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S15" s="34" t="s">
         <v>831</v>
       </c>
-      <c r="U15" s="35" t="s">
+      <c r="T15" s="34" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -4437,38 +4465,35 @@
       <c r="K16" t="s">
         <v>179</v>
       </c>
-      <c r="L16" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N16" s="19" t="s">
+      <c r="L16" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M16" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O16" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P16" s="25" t="s">
+      <c r="N16" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O16" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q16" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R16" s="31" t="s">
+      <c r="P16" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q16" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S16" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T16" s="35" t="s">
+      <c r="R16" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S16" s="34" t="s">
         <v>830</v>
       </c>
-      <c r="U16" s="35" t="s">
+      <c r="T16" s="34" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -4502,38 +4527,35 @@
       <c r="K17" t="s">
         <v>179</v>
       </c>
-      <c r="L17" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N17" s="19" t="s">
+      <c r="L17" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M17" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O17" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P17" s="25" t="s">
+      <c r="N17" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O17" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q17" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R17" s="31" t="s">
+      <c r="P17" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q17" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S17" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T17" s="34" t="s">
+      <c r="R17" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S17" s="33" t="s">
         <v>821</v>
       </c>
-      <c r="U17" s="34" t="s">
+      <c r="T17" s="33" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>429</v>
       </c>
@@ -4567,38 +4589,35 @@
       <c r="K18" t="s">
         <v>179</v>
       </c>
-      <c r="L18" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N18" s="19" t="s">
+      <c r="L18" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M18" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O18" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P18" s="25" t="s">
+      <c r="N18" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O18" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q18" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R18" s="31" t="s">
+      <c r="P18" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q18" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S18" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T18" s="35" t="s">
+      <c r="R18" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S18" s="34" t="s">
         <v>829</v>
       </c>
-      <c r="U18" s="35" t="s">
+      <c r="T18" s="34" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -4632,38 +4651,35 @@
       <c r="K19" t="s">
         <v>179</v>
       </c>
-      <c r="L19" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N19" s="19" t="s">
+      <c r="L19" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M19" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O19" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P19" s="25" t="s">
+      <c r="N19" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O19" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q19" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R19" s="31" t="s">
+      <c r="P19" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q19" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S19" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T19" s="35" t="s">
+      <c r="R19" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S19" s="34" t="s">
         <v>828</v>
       </c>
-      <c r="U19" s="35" t="s">
+      <c r="T19" s="34" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -4697,103 +4713,97 @@
       <c r="K20" t="s">
         <v>179</v>
       </c>
-      <c r="L20" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N20" s="19" t="s">
+      <c r="L20" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M20" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O20" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P20" s="25" t="s">
+      <c r="N20" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O20" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q20" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R20" s="31" t="s">
+      <c r="P20" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q20" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S20" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T20" s="35" t="s">
+      <c r="R20" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S20" s="34" t="s">
         <v>822</v>
       </c>
-      <c r="U20" s="35" t="s">
+      <c r="T20" s="34" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>348</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="L21" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N21" s="19" t="s">
+      <c r="L21" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M21" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O21" s="17" t="s">
-        <v>732</v>
-      </c>
-      <c r="P21" s="25" t="s">
+      <c r="N21" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="O21" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q21" s="23" t="s">
-        <v>732</v>
-      </c>
-      <c r="R21" s="31" t="s">
+      <c r="P21" s="22" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q21" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S21" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T21" s="36" t="s">
+      <c r="R21" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S21" s="35" t="s">
         <v>820</v>
       </c>
-      <c r="U21" s="40" t="s">
+      <c r="T21" s="39" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>78</v>
       </c>
@@ -4827,38 +4837,35 @@
       <c r="K22" t="s">
         <v>179</v>
       </c>
-      <c r="L22" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N22" s="19" t="s">
+      <c r="L22" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M22" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O22" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P22" s="25" t="s">
+      <c r="N22" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O22" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q22" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R22" s="31" t="s">
+      <c r="P22" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q22" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S22" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T22" s="35" t="s">
+      <c r="R22" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S22" s="34" t="s">
         <v>823</v>
       </c>
-      <c r="U22" s="35" t="s">
+      <c r="T22" s="34" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -4892,38 +4899,35 @@
       <c r="K23" t="s">
         <v>179</v>
       </c>
-      <c r="L23" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N23" s="19" t="s">
+      <c r="L23" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M23" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O23" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P23" s="25" t="s">
+      <c r="N23" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O23" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q23" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R23" s="31" t="s">
+      <c r="P23" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q23" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S23" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T23" s="35" t="s">
+      <c r="R23" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S23" s="34" t="s">
         <v>824</v>
       </c>
-      <c r="U23" s="35" t="s">
+      <c r="T23" s="34" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -4957,38 +4961,35 @@
       <c r="K24" t="s">
         <v>179</v>
       </c>
-      <c r="L24" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N24" s="19" t="s">
+      <c r="L24" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M24" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O24" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P24" s="25" t="s">
+      <c r="N24" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O24" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q24" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R24" s="31" t="s">
+      <c r="P24" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q24" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S24" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T24" s="35" t="s">
+      <c r="R24" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S24" s="34" t="s">
         <v>825</v>
       </c>
-      <c r="U24" s="35" t="s">
+      <c r="T24" s="34" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>422</v>
       </c>
@@ -5022,38 +5023,35 @@
       <c r="K25" t="s">
         <v>179</v>
       </c>
-      <c r="L25" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N25" s="19" t="s">
+      <c r="L25" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M25" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O25" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P25" s="25" t="s">
+      <c r="N25" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O25" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q25" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R25" s="31" t="s">
+      <c r="P25" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q25" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S25" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T25" s="35" t="s">
+      <c r="R25" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S25" s="34" t="s">
         <v>827</v>
       </c>
-      <c r="U25" s="35" t="s">
+      <c r="T25" s="34" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -5087,38 +5085,35 @@
       <c r="K26" t="s">
         <v>179</v>
       </c>
-      <c r="L26" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N26" s="19" t="s">
+      <c r="L26" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M26" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O26" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P26" s="25" t="s">
+      <c r="N26" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O26" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q26" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R26" s="31" t="s">
+      <c r="P26" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q26" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="S26" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T26" s="35" t="s">
+      <c r="R26" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S26" s="34" t="s">
         <v>826</v>
       </c>
-      <c r="U26" s="35" t="s">
+      <c r="T26" s="34" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -5152,103 +5147,97 @@
       <c r="K27" t="s">
         <v>179</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M27" s="18" t="s">
         <v>751</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="N27" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O27" s="24" t="s">
         <v>751</v>
       </c>
-      <c r="N27" s="19" t="s">
+      <c r="P27" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q27" s="30" t="s">
         <v>751</v>
       </c>
-      <c r="O27" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P27" s="25" t="s">
+      <c r="R27" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S27" s="35" t="s">
         <v>751</v>
       </c>
-      <c r="Q27" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R27" s="31" t="s">
-        <v>751</v>
-      </c>
-      <c r="S27" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T27" s="36" t="s">
-        <v>751</v>
-      </c>
-      <c r="U27" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="13" t="s">
+      <c r="T27" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="12" t="s">
         <v>640</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="12" t="s">
         <v>641</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="12" t="s">
         <v>642</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="12" t="s">
         <v>643</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="13" t="s">
         <v>721</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H28" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="12" t="s">
         <v>644</v>
       </c>
-      <c r="J28" s="13" t="s">
+      <c r="J28" s="12" t="s">
         <v>645</v>
       </c>
-      <c r="K28" s="13" t="s">
+      <c r="K28" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N28" s="18" t="s">
-        <v>732</v>
-      </c>
-      <c r="O28" s="18" t="s">
-        <v>732</v>
-      </c>
-      <c r="P28" s="24" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q28" s="24" t="s">
-        <v>732</v>
-      </c>
-      <c r="R28" s="30" t="s">
-        <v>732</v>
-      </c>
-      <c r="S28" s="30" t="s">
-        <v>732</v>
-      </c>
-      <c r="T28" s="39" t="s">
-        <v>732</v>
-      </c>
-      <c r="U28" s="39" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="L28" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M28" s="17" t="s">
+        <v>732</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>732</v>
+      </c>
+      <c r="O28" s="23" t="s">
+        <v>732</v>
+      </c>
+      <c r="P28" s="23" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q28" s="29" t="s">
+        <v>732</v>
+      </c>
+      <c r="R28" s="29" t="s">
+        <v>732</v>
+      </c>
+      <c r="S28" s="38" t="s">
+        <v>732</v>
+      </c>
+      <c r="T28" s="38" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -5282,38 +5271,35 @@
       <c r="K29" t="s">
         <v>179</v>
       </c>
-      <c r="L29" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N29" s="19" t="s">
+      <c r="L29" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M29" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O29" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P29" s="25" t="s">
+      <c r="N29" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O29" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q29" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R29" s="31" t="s">
+      <c r="P29" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q29" s="30" t="s">
         <v>774</v>
       </c>
-      <c r="S29" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T29" s="35" t="s">
+      <c r="R29" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S29" s="34" t="s">
         <v>832</v>
       </c>
-      <c r="U29" s="35" t="s">
+      <c r="T29" s="34" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>634</v>
       </c>
@@ -5347,38 +5333,35 @@
       <c r="K30" t="s">
         <v>179</v>
       </c>
-      <c r="L30" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N30" s="19" t="s">
+      <c r="L30" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M30" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O30" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P30" s="25" t="s">
+      <c r="N30" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O30" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q30" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R30" s="31" t="s">
+      <c r="P30" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q30" s="30" t="s">
         <v>774</v>
       </c>
-      <c r="S30" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T30" s="35" t="s">
+      <c r="R30" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S30" s="34" t="s">
         <v>833</v>
       </c>
-      <c r="U30" s="35" t="s">
+      <c r="T30" s="34" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>622</v>
       </c>
@@ -5412,38 +5395,35 @@
       <c r="K31" t="s">
         <v>179</v>
       </c>
-      <c r="L31" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N31" s="19" t="s">
+      <c r="L31" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M31" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O31" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P31" s="25" t="s">
+      <c r="N31" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O31" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q31" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R31" s="31" t="s">
+      <c r="P31" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q31" s="30" t="s">
         <v>774</v>
       </c>
-      <c r="S31" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T31" s="35" t="s">
+      <c r="R31" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S31" s="34" t="s">
         <v>834</v>
       </c>
-      <c r="U31" s="35" t="s">
+      <c r="T31" s="34" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>628</v>
       </c>
@@ -5477,38 +5457,35 @@
       <c r="K32" t="s">
         <v>179</v>
       </c>
-      <c r="L32" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N32" s="19" t="s">
+      <c r="L32" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M32" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O32" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P32" s="25" t="s">
+      <c r="N32" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O32" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q32" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R32" s="31" t="s">
+      <c r="P32" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q32" s="30" t="s">
         <v>774</v>
       </c>
-      <c r="S32" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T32" s="35" t="s">
+      <c r="R32" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S32" s="34" t="s">
         <v>835</v>
       </c>
-      <c r="U32" s="35" t="s">
+      <c r="T32" s="34" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>616</v>
       </c>
@@ -5542,38 +5519,35 @@
       <c r="K33" t="s">
         <v>179</v>
       </c>
-      <c r="L33" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N33" s="19" t="s">
+      <c r="L33" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M33" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O33" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P33" s="25" t="s">
+      <c r="N33" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O33" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q33" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R33" s="31" t="s">
+      <c r="P33" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q33" s="30" t="s">
         <v>774</v>
       </c>
-      <c r="S33" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T33" s="35" t="s">
+      <c r="R33" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S33" s="34" t="s">
         <v>836</v>
       </c>
-      <c r="U33" s="35" t="s">
+      <c r="T33" s="34" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>506</v>
       </c>
@@ -5607,38 +5581,35 @@
       <c r="K34" t="s">
         <v>179</v>
       </c>
-      <c r="L34" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N34" s="19" t="s">
+      <c r="L34" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M34" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O34" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P34" s="25" t="s">
+      <c r="N34" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O34" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q34" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R34" s="31" t="s">
+      <c r="P34" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q34" s="30" t="s">
         <v>774</v>
       </c>
-      <c r="S34" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T34" s="36" t="s">
-        <v>732</v>
-      </c>
-      <c r="U34" s="40" t="s">
+      <c r="R34" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S34" s="35" t="s">
+        <v>732</v>
+      </c>
+      <c r="T34" s="39" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -5672,38 +5643,35 @@
       <c r="K35" t="s">
         <v>179</v>
       </c>
-      <c r="L35" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N35" s="19" t="s">
+      <c r="L35" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M35" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O35" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P35" s="25" t="s">
+      <c r="N35" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O35" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q35" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R35" s="31" t="s">
+      <c r="P35" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q35" s="30" t="s">
         <v>774</v>
       </c>
-      <c r="S35" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T35" s="35" t="s">
+      <c r="R35" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S35" s="34" t="s">
         <v>837</v>
       </c>
-      <c r="U35" s="35" t="s">
+      <c r="T35" s="34" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -5737,38 +5705,35 @@
       <c r="K36" t="s">
         <v>179</v>
       </c>
-      <c r="L36" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N36" s="19" t="s">
+      <c r="L36" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M36" s="18" t="s">
         <v>774</v>
       </c>
-      <c r="O36" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P36" s="25" t="s">
+      <c r="N36" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O36" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="Q36" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R36" s="31" t="s">
+      <c r="P36" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q36" s="30" t="s">
         <v>774</v>
       </c>
-      <c r="S36" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T36" s="36" t="s">
+      <c r="R36" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S36" s="35" t="s">
         <v>854</v>
       </c>
-      <c r="U36" s="40" t="s">
+      <c r="T36" s="39" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>492</v>
       </c>
@@ -5802,38 +5767,35 @@
       <c r="K37" t="s">
         <v>179</v>
       </c>
-      <c r="L37" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N37" s="19" t="s">
+      <c r="L37" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="M37" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="O37" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P37" s="25" t="s">
+      <c r="N37" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O37" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="Q37" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R37" s="28" t="s">
+      <c r="P37" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q37" s="27" t="s">
         <v>800</v>
       </c>
-      <c r="S37" s="28" t="s">
+      <c r="R37" s="27" t="s">
         <v>800</v>
       </c>
-      <c r="T37" s="36" t="s">
+      <c r="S37" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="U37" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T37" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>94</v>
       </c>
@@ -5867,38 +5829,35 @@
       <c r="K38" t="s">
         <v>179</v>
       </c>
-      <c r="L38" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N38" s="19" t="s">
+      <c r="L38" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="M38" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="O38" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P38" s="25" t="s">
+      <c r="N38" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O38" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="Q38" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R38" s="29" t="s">
+      <c r="P38" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q38" s="28" t="s">
         <v>801</v>
       </c>
-      <c r="S38" s="29" t="s">
+      <c r="R38" s="28" t="s">
         <v>801</v>
       </c>
-      <c r="T38" s="36" t="s">
+      <c r="S38" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="U38" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T38" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>96</v>
       </c>
@@ -5932,38 +5891,35 @@
       <c r="K39" t="s">
         <v>179</v>
       </c>
-      <c r="L39" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N39" s="19" t="s">
+      <c r="L39" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="M39" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="O39" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P39" s="25" t="s">
+      <c r="N39" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O39" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="Q39" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R39" s="29" t="s">
+      <c r="P39" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q39" s="28" t="s">
         <v>802</v>
       </c>
-      <c r="S39" s="29" t="s">
+      <c r="R39" s="28" t="s">
         <v>802</v>
       </c>
-      <c r="T39" s="36" t="s">
+      <c r="S39" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="U39" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T39" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>512</v>
       </c>
@@ -5997,38 +5953,35 @@
       <c r="K40" t="s">
         <v>179</v>
       </c>
-      <c r="L40" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N40" s="19" t="s">
+      <c r="L40" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="M40" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="O40" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P40" s="25" t="s">
+      <c r="N40" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O40" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="Q40" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R40" s="29" t="s">
+      <c r="P40" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q40" s="28" t="s">
         <v>803</v>
       </c>
-      <c r="S40" s="29" t="s">
+      <c r="R40" s="28" t="s">
         <v>803</v>
       </c>
-      <c r="T40" s="36" t="s">
+      <c r="S40" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="U40" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T40" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>100</v>
       </c>
@@ -6041,7 +5994,7 @@
       <c r="D41" t="s">
         <v>398</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="8" t="s">
         <v>159</v>
       </c>
       <c r="F41" t="s">
@@ -6062,103 +6015,97 @@
       <c r="K41" t="s">
         <v>179</v>
       </c>
-      <c r="L41" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N41" s="19" t="s">
+      <c r="L41" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="M41" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="O41" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P41" s="25" t="s">
+      <c r="N41" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O41" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="Q41" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R41" s="28" t="s">
+      <c r="P41" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q41" s="27" t="s">
         <v>804</v>
       </c>
-      <c r="S41" s="28" t="s">
+      <c r="R41" s="27" t="s">
         <v>804</v>
       </c>
-      <c r="T41" s="36" t="s">
+      <c r="S41" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="U41" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="5" t="s">
+      <c r="T41" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="I42" s="5" t="s">
+      <c r="I42" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="J42" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="K42" s="5" t="s">
+      <c r="K42" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="L42" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M42" s="11" t="s">
-        <v>732</v>
-      </c>
-      <c r="N42" s="19" t="s">
+      <c r="L42" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="M42" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="O42" s="17" t="s">
-        <v>732</v>
-      </c>
-      <c r="P42" s="25" t="s">
+      <c r="N42" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="O42" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="Q42" s="23" t="s">
-        <v>732</v>
-      </c>
-      <c r="R42" s="31" t="s">
+      <c r="P42" s="22" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q42" s="30" t="s">
         <v>805</v>
       </c>
-      <c r="S42" s="40" t="s">
+      <c r="R42" s="39" t="s">
         <v>846</v>
       </c>
-      <c r="T42" s="36" t="s">
+      <c r="S42" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="U42" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T42" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>646</v>
       </c>
@@ -6192,38 +6139,35 @@
       <c r="K43" t="s">
         <v>179</v>
       </c>
-      <c r="L43" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N43" s="19" t="s">
+      <c r="L43" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="M43" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="O43" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P43" s="25" t="s">
+      <c r="N43" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O43" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="Q43" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R43" s="29" t="s">
+      <c r="P43" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q43" s="28" t="s">
         <v>806</v>
       </c>
-      <c r="S43" s="29" t="s">
+      <c r="R43" s="28" t="s">
         <v>806</v>
       </c>
-      <c r="T43" s="36" t="s">
+      <c r="S43" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="U43" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T43" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>92</v>
       </c>
@@ -6257,38 +6201,35 @@
       <c r="K44" t="s">
         <v>179</v>
       </c>
-      <c r="L44" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N44" s="19" t="s">
+      <c r="L44" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="M44" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="O44" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P44" s="25" t="s">
+      <c r="N44" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O44" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="Q44" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R44" s="29" t="s">
+      <c r="P44" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q44" s="28" t="s">
         <v>807</v>
       </c>
-      <c r="S44" s="29" t="s">
+      <c r="R44" s="28" t="s">
         <v>807</v>
       </c>
-      <c r="T44" s="36" t="s">
+      <c r="S44" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="U44" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T44" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>585</v>
       </c>
@@ -6322,38 +6263,35 @@
       <c r="K45" t="s">
         <v>179</v>
       </c>
-      <c r="L45" s="12" t="s">
+      <c r="L45" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="M45" s="15" t="s">
         <v>752</v>
       </c>
-      <c r="M45" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N45" s="16" t="s">
+      <c r="N45" s="15" t="s">
         <v>752</v>
       </c>
-      <c r="O45" s="16" t="s">
+      <c r="O45" s="21" t="s">
         <v>752</v>
       </c>
-      <c r="P45" s="22" t="s">
+      <c r="P45" s="21" t="s">
         <v>752</v>
       </c>
-      <c r="Q45" s="22" t="s">
+      <c r="Q45" s="30" t="s">
         <v>752</v>
       </c>
-      <c r="R45" s="31" t="s">
+      <c r="R45" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S45" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="S45" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T45" s="36" t="s">
-        <v>752</v>
-      </c>
-      <c r="U45" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T45" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>104</v>
       </c>
@@ -6387,38 +6325,35 @@
       <c r="K46" t="s">
         <v>179</v>
       </c>
-      <c r="L46" s="12" t="s">
+      <c r="L46" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="M46" s="15" t="s">
         <v>752</v>
       </c>
-      <c r="M46" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N46" s="16" t="s">
+      <c r="N46" s="15" t="s">
         <v>752</v>
       </c>
-      <c r="O46" s="16" t="s">
+      <c r="O46" s="21" t="s">
         <v>752</v>
       </c>
-      <c r="P46" s="22" t="s">
+      <c r="P46" s="21" t="s">
         <v>752</v>
       </c>
-      <c r="Q46" s="22" t="s">
+      <c r="Q46" s="30" t="s">
         <v>752</v>
       </c>
-      <c r="R46" s="31" t="s">
+      <c r="R46" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S46" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="S46" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T46" s="36" t="s">
-        <v>752</v>
-      </c>
-      <c r="U46" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T46" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>652</v>
       </c>
@@ -6453,37 +6388,34 @@
         <v>179</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N47" s="19" t="s">
-        <v>732</v>
-      </c>
-      <c r="O47" s="40" t="s">
+        <v>939</v>
+      </c>
+      <c r="M47" s="18" t="s">
+        <v>732</v>
+      </c>
+      <c r="N47" s="39" t="s">
         <v>844</v>
       </c>
-      <c r="P47" s="25" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q47" s="40" t="s">
+      <c r="O47" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="P47" s="39" t="s">
         <v>844</v>
       </c>
-      <c r="R47" s="31" t="s">
-        <v>732</v>
-      </c>
-      <c r="S47" s="40" t="s">
+      <c r="Q47" s="30" t="s">
+        <v>732</v>
+      </c>
+      <c r="R47" s="39" t="s">
         <v>844</v>
       </c>
-      <c r="T47" s="36" t="s">
-        <v>732</v>
-      </c>
-      <c r="U47" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="S47" s="35" t="s">
+        <v>732</v>
+      </c>
+      <c r="T47" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -6496,7 +6428,7 @@
       <c r="D48" t="s">
         <v>403</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E48" s="8" t="s">
         <v>160</v>
       </c>
       <c r="F48" t="s">
@@ -6517,38 +6449,35 @@
       <c r="K48" t="s">
         <v>179</v>
       </c>
-      <c r="L48" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N48" s="19" t="s">
+      <c r="L48" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="M48" s="18" t="s">
         <v>752</v>
       </c>
-      <c r="O48" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P48" s="22" t="s">
+      <c r="N48" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O48" s="21" t="s">
         <v>752</v>
       </c>
-      <c r="Q48" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R48" s="31" t="s">
+      <c r="P48" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q48" s="30" t="s">
         <v>808</v>
       </c>
-      <c r="S48" s="40" t="s">
+      <c r="R48" s="39" t="s">
         <v>847</v>
       </c>
-      <c r="T48" s="36" t="s">
+      <c r="S48" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="U48" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T48" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>106</v>
       </c>
@@ -6582,38 +6511,35 @@
       <c r="K49" t="s">
         <v>179</v>
       </c>
-      <c r="L49" s="12" t="s">
+      <c r="L49" s="11" t="s">
+        <v>945</v>
+      </c>
+      <c r="M49" s="15" t="s">
         <v>753</v>
       </c>
-      <c r="M49" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N49" s="16" t="s">
+      <c r="N49" s="15" t="s">
         <v>753</v>
       </c>
-      <c r="O49" s="16" t="s">
+      <c r="O49" s="21" t="s">
         <v>753</v>
       </c>
-      <c r="P49" s="22" t="s">
+      <c r="P49" s="21" t="s">
         <v>753</v>
       </c>
-      <c r="Q49" s="22" t="s">
+      <c r="Q49" s="27" t="s">
         <v>753</v>
       </c>
-      <c r="R49" s="28" t="s">
+      <c r="R49" s="27" t="s">
         <v>753</v>
       </c>
-      <c r="S49" s="28" t="s">
+      <c r="S49" s="35" t="s">
         <v>753</v>
       </c>
-      <c r="T49" s="36" t="s">
-        <v>753</v>
-      </c>
-      <c r="U49" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T49" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>579</v>
       </c>
@@ -6647,38 +6573,35 @@
       <c r="K50" t="s">
         <v>179</v>
       </c>
-      <c r="L50" s="12" t="s">
+      <c r="L50" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="M50" s="15" t="s">
         <v>754</v>
       </c>
-      <c r="M50" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N50" s="16" t="s">
+      <c r="N50" s="15" t="s">
         <v>754</v>
       </c>
-      <c r="O50" s="16" t="s">
+      <c r="O50" s="21" t="s">
         <v>754</v>
       </c>
-      <c r="P50" s="22" t="s">
+      <c r="P50" s="21" t="s">
         <v>754</v>
       </c>
-      <c r="Q50" s="22" t="s">
+      <c r="Q50" s="30" t="s">
         <v>754</v>
       </c>
-      <c r="R50" s="31" t="s">
+      <c r="R50" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S50" s="35" t="s">
         <v>754</v>
       </c>
-      <c r="S50" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T50" s="36" t="s">
-        <v>754</v>
-      </c>
-      <c r="U50" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T50" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>478</v>
       </c>
@@ -6712,38 +6635,35 @@
       <c r="K51" t="s">
         <v>179</v>
       </c>
-      <c r="L51" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N51" s="16" t="s">
+      <c r="L51" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M51" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="O51" s="16" t="s">
+      <c r="N51" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="P51" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q51" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R51" s="31" t="s">
+      <c r="O51" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="P51" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q51" s="30" t="s">
         <v>775</v>
       </c>
-      <c r="S51" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T51" s="36" t="s">
+      <c r="R51" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S51" s="35" t="s">
         <v>775</v>
       </c>
-      <c r="U51" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T51" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>28</v>
       </c>
@@ -6777,38 +6697,35 @@
       <c r="K52" t="s">
         <v>179</v>
       </c>
-      <c r="L52" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N52" s="16" t="s">
+      <c r="L52" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M52" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="O52" s="16" t="s">
+      <c r="N52" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="P52" s="22" t="s">
+      <c r="O52" s="21" t="s">
         <v>790</v>
       </c>
-      <c r="Q52" s="22" t="s">
+      <c r="P52" s="21" t="s">
         <v>790</v>
       </c>
-      <c r="R52" s="31" t="s">
+      <c r="Q52" s="30" t="s">
         <v>775</v>
       </c>
-      <c r="S52" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T52" s="36" t="s">
+      <c r="R52" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S52" s="35" t="s">
         <v>775</v>
       </c>
-      <c r="U52" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T52" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -6842,38 +6759,35 @@
       <c r="K53" t="s">
         <v>179</v>
       </c>
-      <c r="L53" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N53" s="16" t="s">
+      <c r="L53" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M53" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="O53" s="16" t="s">
+      <c r="N53" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="P53" s="22" t="s">
+      <c r="O53" s="21" t="s">
         <v>791</v>
       </c>
-      <c r="Q53" s="22" t="s">
+      <c r="P53" s="21" t="s">
         <v>791</v>
       </c>
-      <c r="R53" s="31" t="s">
+      <c r="Q53" s="30" t="s">
         <v>775</v>
       </c>
-      <c r="S53" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T53" s="36" t="s">
+      <c r="R53" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S53" s="35" t="s">
         <v>775</v>
       </c>
-      <c r="U53" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T53" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>537</v>
       </c>
@@ -6908,37 +6822,34 @@
         <v>179</v>
       </c>
       <c r="L54" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="M54" s="15" t="s">
         <v>755</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="N54" s="15" t="s">
         <v>755</v>
       </c>
-      <c r="N54" s="16" t="s">
+      <c r="O54" s="21" t="s">
         <v>755</v>
       </c>
-      <c r="O54" s="16" t="s">
+      <c r="P54" s="21" t="s">
         <v>755</v>
       </c>
-      <c r="P54" s="22" t="s">
+      <c r="Q54" s="27" t="s">
         <v>755</v>
       </c>
-      <c r="Q54" s="22" t="s">
+      <c r="R54" s="27" t="s">
         <v>755</v>
       </c>
-      <c r="R54" s="28" t="s">
+      <c r="S54" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="S54" s="28" t="s">
+      <c r="T54" s="33" t="s">
         <v>755</v>
       </c>
-      <c r="T54" s="34" t="s">
-        <v>755</v>
-      </c>
-      <c r="U54" s="34" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>549</v>
       </c>
@@ -6973,37 +6884,34 @@
         <v>179</v>
       </c>
       <c r="L55" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="M55" s="15" t="s">
         <v>756</v>
       </c>
-      <c r="M55" s="2" t="s">
+      <c r="N55" s="15" t="s">
         <v>756</v>
       </c>
-      <c r="N55" s="16" t="s">
+      <c r="O55" s="21" t="s">
         <v>756</v>
       </c>
-      <c r="O55" s="16" t="s">
+      <c r="P55" s="21" t="s">
         <v>756</v>
       </c>
-      <c r="P55" s="22" t="s">
+      <c r="Q55" s="27" t="s">
         <v>756</v>
       </c>
-      <c r="Q55" s="22" t="s">
+      <c r="R55" s="27" t="s">
         <v>756</v>
       </c>
-      <c r="R55" s="28" t="s">
+      <c r="S55" s="33" t="s">
         <v>756</v>
       </c>
-      <c r="S55" s="28" t="s">
+      <c r="T55" s="33" t="s">
         <v>756</v>
       </c>
-      <c r="T55" s="34" t="s">
-        <v>756</v>
-      </c>
-      <c r="U55" s="34" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>543</v>
       </c>
@@ -7037,168 +6945,159 @@
       <c r="K56" t="s">
         <v>179</v>
       </c>
-      <c r="L56" s="12" t="s">
+      <c r="L56" s="11" t="s">
+        <v>944</v>
+      </c>
+      <c r="M56" s="15" t="s">
         <v>757</v>
       </c>
-      <c r="M56" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N56" s="16" t="s">
+      <c r="N56" s="15" t="s">
         <v>757</v>
       </c>
-      <c r="O56" s="16" t="s">
+      <c r="O56" s="21" t="s">
         <v>757</v>
       </c>
-      <c r="P56" s="22" t="s">
+      <c r="P56" s="21" t="s">
         <v>757</v>
       </c>
-      <c r="Q56" s="22" t="s">
+      <c r="Q56" s="27" t="s">
         <v>757</v>
       </c>
-      <c r="R56" s="28" t="s">
+      <c r="R56" s="27" t="s">
         <v>757</v>
       </c>
-      <c r="S56" s="28" t="s">
+      <c r="S56" s="33" t="s">
         <v>757</v>
       </c>
-      <c r="T56" s="34" t="s">
+      <c r="T56" s="33" t="s">
         <v>757</v>
       </c>
-      <c r="U56" s="34" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="4" t="s">
+    </row>
+    <row r="57" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="3" t="s">
         <v>249</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="H57" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="I57" s="4" t="s">
+      <c r="I57" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="J57" s="4" t="s">
+      <c r="J57" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="K57" s="4" t="s">
+      <c r="K57" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="L57" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N57" s="17" t="s">
+      <c r="L57" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M57" s="16" t="s">
         <v>792</v>
       </c>
-      <c r="O57" s="17" t="s">
+      <c r="N57" s="16" t="s">
         <v>792</v>
       </c>
-      <c r="P57" s="22" t="s">
+      <c r="O57" s="21" t="s">
         <v>796</v>
       </c>
-      <c r="Q57" s="22" t="s">
+      <c r="P57" s="21" t="s">
         <v>796</v>
       </c>
-      <c r="R57" s="31" t="s">
+      <c r="Q57" s="30" t="s">
         <v>792</v>
       </c>
-      <c r="S57" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T57" s="36" t="s">
+      <c r="R57" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S57" s="35" t="s">
         <v>792</v>
       </c>
-      <c r="U57" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="4" t="s">
+      <c r="T57" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="3" t="s">
         <v>249</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G58" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H58" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="I58" s="4" t="s">
+      <c r="I58" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="J58" s="4" t="s">
+      <c r="J58" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="K58" s="4" t="s">
+      <c r="K58" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="L58" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N58" s="17" t="s">
+      <c r="L58" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M58" s="16" t="s">
         <v>794</v>
       </c>
-      <c r="O58" s="17" t="s">
+      <c r="N58" s="16" t="s">
         <v>794</v>
       </c>
-      <c r="P58" s="22" t="s">
+      <c r="O58" s="21" t="s">
         <v>793</v>
       </c>
-      <c r="Q58" s="22" t="s">
+      <c r="P58" s="21" t="s">
         <v>793</v>
       </c>
-      <c r="R58" s="31" t="s">
+      <c r="Q58" s="30" t="s">
         <v>794</v>
       </c>
-      <c r="S58" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T58" s="36" t="s">
+      <c r="R58" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S58" s="35" t="s">
         <v>794</v>
       </c>
-      <c r="U58" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T58" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>30</v>
       </c>
@@ -7232,38 +7131,35 @@
       <c r="K59" t="s">
         <v>179</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N59" s="20" t="s">
+      <c r="L59" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M59" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="O59" s="20" t="s">
+      <c r="N59" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="P59" s="26" t="s">
+      <c r="O59" s="25" t="s">
         <v>795</v>
       </c>
-      <c r="Q59" s="26" t="s">
+      <c r="P59" s="25" t="s">
         <v>795</v>
       </c>
-      <c r="R59" s="33" t="s">
+      <c r="Q59" s="32" t="s">
         <v>795</v>
       </c>
-      <c r="S59" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T59" s="37" t="s">
+      <c r="R59" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S59" s="36" t="s">
         <v>795</v>
       </c>
-      <c r="U59" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T59" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>465</v>
       </c>
@@ -7297,38 +7193,35 @@
       <c r="K60" t="s">
         <v>179</v>
       </c>
-      <c r="L60" s="12" t="s">
+      <c r="L60" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="M60" s="15" t="s">
         <v>760</v>
       </c>
-      <c r="M60" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N60" s="16" t="s">
+      <c r="N60" s="39" t="s">
+        <v>845</v>
+      </c>
+      <c r="O60" s="22" t="s">
         <v>760</v>
       </c>
-      <c r="O60" s="40" t="s">
+      <c r="P60" s="39" t="s">
         <v>845</v>
       </c>
-      <c r="P60" s="23" t="s">
+      <c r="Q60" s="30" t="s">
         <v>760</v>
       </c>
-      <c r="Q60" s="40" t="s">
-        <v>845</v>
-      </c>
-      <c r="R60" s="31" t="s">
+      <c r="R60" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S60" s="35" t="s">
         <v>760</v>
       </c>
-      <c r="S60" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T60" s="36" t="s">
-        <v>760</v>
-      </c>
-      <c r="U60" s="40" t="s">
+      <c r="T60" s="39" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -7362,38 +7255,35 @@
       <c r="K61" t="s">
         <v>179</v>
       </c>
-      <c r="L61" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N61" s="16" t="s">
+      <c r="L61" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M61" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="O61" s="16" t="s">
+      <c r="N61" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="P61" s="25" t="s">
+      <c r="O61" s="24" t="s">
         <v>776</v>
       </c>
-      <c r="Q61" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R61" s="31" t="s">
+      <c r="P61" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q61" s="30" t="s">
         <v>776</v>
       </c>
-      <c r="S61" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T61" s="36" t="s">
+      <c r="R61" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S61" s="35" t="s">
         <v>776</v>
       </c>
-      <c r="U61" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T61" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>24</v>
       </c>
@@ -7427,38 +7317,35 @@
       <c r="K62" t="s">
         <v>179</v>
       </c>
-      <c r="L62" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N62" s="16" t="s">
+      <c r="L62" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M62" s="15" t="s">
         <v>774</v>
       </c>
-      <c r="O62" s="16" t="s">
+      <c r="N62" s="15" t="s">
         <v>774</v>
       </c>
-      <c r="P62" s="22" t="s">
+      <c r="O62" s="21" t="s">
         <v>788</v>
       </c>
-      <c r="Q62" s="22" t="s">
+      <c r="P62" s="21" t="s">
         <v>788</v>
       </c>
-      <c r="R62" s="31" t="s">
+      <c r="Q62" s="30" t="s">
         <v>774</v>
       </c>
-      <c r="S62" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T62" s="36" t="s">
+      <c r="R62" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S62" s="35" t="s">
         <v>774</v>
       </c>
-      <c r="U62" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T62" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>555</v>
       </c>
@@ -7493,37 +7380,34 @@
         <v>179</v>
       </c>
       <c r="L63" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="M63" s="15" t="s">
         <v>761</v>
       </c>
-      <c r="M63" s="2" t="s">
+      <c r="N63" s="15" t="s">
         <v>761</v>
       </c>
-      <c r="N63" s="16" t="s">
+      <c r="O63" s="21" t="s">
         <v>761</v>
       </c>
-      <c r="O63" s="16" t="s">
+      <c r="P63" s="21" t="s">
         <v>761</v>
       </c>
-      <c r="P63" s="22" t="s">
+      <c r="Q63" s="30" t="s">
         <v>761</v>
       </c>
-      <c r="Q63" s="22" t="s">
+      <c r="R63" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S63" s="35" t="s">
         <v>761</v>
       </c>
-      <c r="R63" s="31" t="s">
-        <v>761</v>
-      </c>
-      <c r="S63" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T63" s="36" t="s">
-        <v>761</v>
-      </c>
-      <c r="U63" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T63" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>531</v>
       </c>
@@ -7558,37 +7442,34 @@
         <v>179</v>
       </c>
       <c r="L64" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="M64" s="15" t="s">
         <v>762</v>
       </c>
-      <c r="M64" s="2" t="s">
+      <c r="N64" s="15" t="s">
         <v>762</v>
       </c>
-      <c r="N64" s="16" t="s">
+      <c r="O64" s="21" t="s">
         <v>762</v>
       </c>
-      <c r="O64" s="16" t="s">
+      <c r="P64" s="21" t="s">
         <v>762</v>
       </c>
-      <c r="P64" s="22" t="s">
+      <c r="Q64" s="30" t="s">
         <v>762</v>
       </c>
-      <c r="Q64" s="22" t="s">
+      <c r="R64" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S64" s="35" t="s">
         <v>762</v>
       </c>
-      <c r="R64" s="31" t="s">
-        <v>762</v>
-      </c>
-      <c r="S64" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T64" s="36" t="s">
-        <v>762</v>
-      </c>
-      <c r="U64" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T64" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -7622,38 +7503,35 @@
       <c r="K65" t="s">
         <v>179</v>
       </c>
-      <c r="L65" s="12" t="s">
+      <c r="L65" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="M65" s="15" t="s">
         <v>763</v>
       </c>
-      <c r="M65" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N65" s="16" t="s">
+      <c r="N65" s="15" t="s">
         <v>763</v>
       </c>
-      <c r="O65" s="16" t="s">
+      <c r="O65" s="21" t="s">
         <v>763</v>
       </c>
-      <c r="P65" s="22" t="s">
+      <c r="P65" s="21" t="s">
         <v>763</v>
       </c>
-      <c r="Q65" s="22" t="s">
+      <c r="Q65" s="27" t="s">
         <v>763</v>
       </c>
-      <c r="R65" s="28" t="s">
+      <c r="R65" s="27" t="s">
         <v>763</v>
       </c>
-      <c r="S65" s="28" t="s">
+      <c r="S65" s="35" t="s">
         <v>763</v>
       </c>
-      <c r="T65" s="36" t="s">
-        <v>763</v>
-      </c>
-      <c r="U65" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T65" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>573</v>
       </c>
@@ -7688,37 +7566,34 @@
         <v>179</v>
       </c>
       <c r="L66" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="M66" s="15" t="s">
         <v>764</v>
       </c>
-      <c r="M66" s="2" t="s">
+      <c r="N66" s="15" t="s">
         <v>764</v>
       </c>
-      <c r="N66" s="16" t="s">
+      <c r="O66" s="21" t="s">
         <v>764</v>
       </c>
-      <c r="O66" s="16" t="s">
+      <c r="P66" s="21" t="s">
         <v>764</v>
       </c>
-      <c r="P66" s="22" t="s">
+      <c r="Q66" s="27" t="s">
         <v>764</v>
       </c>
-      <c r="Q66" s="22" t="s">
+      <c r="R66" s="27" t="s">
         <v>764</v>
       </c>
-      <c r="R66" s="28" t="s">
+      <c r="S66" s="35" t="s">
         <v>764</v>
       </c>
-      <c r="S66" s="28" t="s">
-        <v>764</v>
-      </c>
-      <c r="T66" s="36" t="s">
-        <v>764</v>
-      </c>
-      <c r="U66" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T66" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -7752,38 +7627,35 @@
       <c r="K67" t="s">
         <v>179</v>
       </c>
-      <c r="L67" s="11" t="s">
+      <c r="L67" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M67" s="18" t="s">
         <v>751</v>
       </c>
-      <c r="M67" s="11" t="s">
+      <c r="N67" s="39" t="s">
+        <v>842</v>
+      </c>
+      <c r="O67" s="24" t="s">
         <v>751</v>
       </c>
-      <c r="N67" s="19" t="s">
+      <c r="P67" s="39" t="s">
+        <v>842</v>
+      </c>
+      <c r="Q67" s="30" t="s">
         <v>751</v>
       </c>
-      <c r="O67" s="40" t="s">
+      <c r="R67" s="39" t="s">
         <v>842</v>
       </c>
-      <c r="P67" s="25" t="s">
+      <c r="S67" s="35" t="s">
         <v>751</v>
       </c>
-      <c r="Q67" s="40" t="s">
+      <c r="T67" s="39" t="s">
         <v>842</v>
       </c>
-      <c r="R67" s="31" t="s">
-        <v>751</v>
-      </c>
-      <c r="S67" s="40" t="s">
-        <v>842</v>
-      </c>
-      <c r="T67" s="36" t="s">
-        <v>751</v>
-      </c>
-      <c r="U67" s="40" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>442</v>
       </c>
@@ -7817,38 +7689,35 @@
       <c r="K68" t="s">
         <v>179</v>
       </c>
-      <c r="L68" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N68" s="16" t="s">
+      <c r="L68" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M68" s="15" t="s">
         <v>777</v>
       </c>
-      <c r="O68" s="16" t="s">
+      <c r="N68" s="15" t="s">
         <v>777</v>
       </c>
-      <c r="P68" s="22" t="s">
+      <c r="O68" s="21" t="s">
         <v>777</v>
       </c>
-      <c r="Q68" s="22" t="s">
+      <c r="P68" s="21" t="s">
         <v>777</v>
       </c>
-      <c r="R68" s="28" t="s">
+      <c r="Q68" s="27" t="s">
         <v>777</v>
       </c>
-      <c r="S68" s="28" t="s">
+      <c r="R68" s="27" t="s">
         <v>777</v>
       </c>
-      <c r="T68" s="34" t="s">
+      <c r="S68" s="33" t="s">
         <v>777</v>
       </c>
-      <c r="U68" s="34" t="s">
+      <c r="T68" s="33" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -7883,37 +7752,34 @@
         <v>179</v>
       </c>
       <c r="L69" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="M69" s="15" t="s">
         <v>765</v>
       </c>
-      <c r="M69" s="2" t="s">
+      <c r="N69" s="15" t="s">
         <v>765</v>
       </c>
-      <c r="N69" s="16" t="s">
+      <c r="O69" s="24" t="s">
         <v>765</v>
       </c>
-      <c r="O69" s="16" t="s">
+      <c r="P69" s="22" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q69" s="30" t="s">
         <v>765</v>
       </c>
-      <c r="P69" s="25" t="s">
+      <c r="R69" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S69" s="35" t="s">
         <v>765</v>
       </c>
-      <c r="Q69" s="23" t="s">
-        <v>732</v>
-      </c>
-      <c r="R69" s="31" t="s">
-        <v>765</v>
-      </c>
-      <c r="S69" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T69" s="36" t="s">
-        <v>765</v>
-      </c>
-      <c r="U69" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T69" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>567</v>
       </c>
@@ -7948,37 +7814,34 @@
         <v>179</v>
       </c>
       <c r="L70" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="M70" s="15" t="s">
         <v>766</v>
       </c>
-      <c r="M70" s="2" t="s">
+      <c r="N70" s="15" t="s">
         <v>766</v>
       </c>
-      <c r="N70" s="16" t="s">
+      <c r="O70" s="21" t="s">
         <v>766</v>
       </c>
-      <c r="O70" s="16" t="s">
+      <c r="P70" s="21" t="s">
         <v>766</v>
       </c>
-      <c r="P70" s="22" t="s">
+      <c r="Q70" s="27" t="s">
         <v>766</v>
       </c>
-      <c r="Q70" s="22" t="s">
+      <c r="R70" s="27" t="s">
         <v>766</v>
       </c>
-      <c r="R70" s="28" t="s">
+      <c r="S70" s="35" t="s">
         <v>766</v>
       </c>
-      <c r="S70" s="28" t="s">
-        <v>766</v>
-      </c>
-      <c r="T70" s="36" t="s">
-        <v>766</v>
-      </c>
-      <c r="U70" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T70" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -8013,37 +7876,34 @@
         <v>179</v>
       </c>
       <c r="L71" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="M71" s="18" t="s">
         <v>767</v>
       </c>
-      <c r="M71" s="2" t="s">
+      <c r="N71" s="39" t="s">
+        <v>843</v>
+      </c>
+      <c r="O71" s="24" t="s">
         <v>767</v>
       </c>
-      <c r="N71" s="19" t="s">
+      <c r="P71" s="39" t="s">
+        <v>843</v>
+      </c>
+      <c r="Q71" s="30" t="s">
         <v>767</v>
       </c>
-      <c r="O71" s="40" t="s">
+      <c r="R71" s="39" t="s">
         <v>843</v>
       </c>
-      <c r="P71" s="25" t="s">
+      <c r="S71" s="35" t="s">
         <v>767</v>
       </c>
-      <c r="Q71" s="40" t="s">
-        <v>843</v>
-      </c>
-      <c r="R71" s="31" t="s">
-        <v>767</v>
-      </c>
-      <c r="S71" s="40" t="s">
-        <v>843</v>
-      </c>
-      <c r="T71" s="36" t="s">
-        <v>767</v>
-      </c>
-      <c r="U71" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T71" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -8077,38 +7937,35 @@
       <c r="K72" t="s">
         <v>179</v>
       </c>
-      <c r="L72" s="12" t="s">
+      <c r="L72" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="M72" s="15" t="s">
         <v>778</v>
       </c>
-      <c r="M72" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N72" s="16" t="s">
+      <c r="N72" s="15" t="s">
         <v>778</v>
       </c>
-      <c r="O72" s="16" t="s">
+      <c r="O72" s="21" t="s">
         <v>778</v>
       </c>
-      <c r="P72" s="22" t="s">
+      <c r="P72" s="21" t="s">
         <v>778</v>
       </c>
-      <c r="Q72" s="22" t="s">
+      <c r="Q72" s="27" t="s">
         <v>778</v>
       </c>
-      <c r="R72" s="28" t="s">
+      <c r="R72" s="27" t="s">
         <v>778</v>
       </c>
-      <c r="S72" s="28" t="s">
+      <c r="S72" s="35" t="s">
         <v>778</v>
       </c>
-      <c r="T72" s="36" t="s">
-        <v>778</v>
-      </c>
-      <c r="U72" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T72" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>36</v>
       </c>
@@ -8142,38 +7999,35 @@
       <c r="K73" t="s">
         <v>179</v>
       </c>
-      <c r="L73" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N73" s="16" t="s">
+      <c r="L73" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M73" s="15" t="s">
         <v>786</v>
       </c>
-      <c r="O73" s="16" t="s">
+      <c r="N73" s="15" t="s">
         <v>786</v>
       </c>
-      <c r="P73" s="22" t="s">
+      <c r="O73" s="21" t="s">
         <v>786</v>
       </c>
-      <c r="Q73" s="22" t="s">
+      <c r="P73" s="21" t="s">
         <v>786</v>
       </c>
-      <c r="R73" s="29" t="s">
+      <c r="Q73" s="28" t="s">
         <v>786</v>
       </c>
-      <c r="S73" s="40" t="s">
+      <c r="R73" s="39" t="s">
         <v>855</v>
       </c>
-      <c r="T73" s="36" t="s">
+      <c r="S73" s="35" t="s">
         <v>786</v>
       </c>
-      <c r="U73" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T73" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>38</v>
       </c>
@@ -8207,38 +8061,35 @@
       <c r="K74" t="s">
         <v>179</v>
       </c>
-      <c r="L74" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M74" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N74" s="16" t="s">
+      <c r="L74" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M74" s="15" t="s">
         <v>785</v>
       </c>
-      <c r="O74" s="16" t="s">
+      <c r="N74" s="15" t="s">
         <v>785</v>
       </c>
-      <c r="P74" s="22" t="s">
+      <c r="O74" s="21" t="s">
         <v>785</v>
       </c>
-      <c r="Q74" s="22" t="s">
+      <c r="P74" s="21" t="s">
         <v>785</v>
       </c>
-      <c r="R74" s="28" t="s">
+      <c r="Q74" s="27" t="s">
         <v>785</v>
       </c>
-      <c r="S74" s="28" t="s">
+      <c r="R74" s="27" t="s">
         <v>785</v>
       </c>
-      <c r="T74" s="36" t="s">
+      <c r="S74" s="35" t="s">
         <v>785</v>
       </c>
-      <c r="U74" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T74" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>40</v>
       </c>
@@ -8272,38 +8123,35 @@
       <c r="K75" t="s">
         <v>179</v>
       </c>
-      <c r="L75" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N75" s="16" t="s">
+      <c r="L75" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M75" s="15" t="s">
         <v>797</v>
       </c>
-      <c r="O75" s="16" t="s">
+      <c r="N75" s="15" t="s">
         <v>797</v>
       </c>
-      <c r="P75" s="22" t="s">
+      <c r="O75" s="21" t="s">
         <v>798</v>
       </c>
-      <c r="Q75" s="22" t="s">
+      <c r="P75" s="21" t="s">
         <v>798</v>
       </c>
-      <c r="R75" s="31" t="s">
+      <c r="Q75" s="30" t="s">
         <v>797</v>
       </c>
-      <c r="S75" s="40" t="s">
+      <c r="R75" s="39" t="s">
         <v>856</v>
       </c>
-      <c r="T75" s="36" t="s">
+      <c r="S75" s="35" t="s">
         <v>797</v>
       </c>
-      <c r="U75" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T75" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>42</v>
       </c>
@@ -8337,38 +8185,35 @@
       <c r="K76" t="s">
         <v>179</v>
       </c>
-      <c r="L76" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N76" s="16" t="s">
+      <c r="L76" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M76" s="15" t="s">
         <v>784</v>
       </c>
-      <c r="O76" s="16" t="s">
+      <c r="N76" s="15" t="s">
         <v>784</v>
       </c>
-      <c r="P76" s="22" t="s">
+      <c r="O76" s="21" t="s">
         <v>784</v>
       </c>
-      <c r="Q76" s="22" t="s">
+      <c r="P76" s="21" t="s">
         <v>784</v>
       </c>
-      <c r="R76" s="29" t="s">
+      <c r="Q76" s="28" t="s">
         <v>784</v>
       </c>
-      <c r="S76" s="29" t="s">
+      <c r="R76" s="28" t="s">
         <v>784</v>
       </c>
-      <c r="T76" s="36" t="s">
+      <c r="S76" s="35" t="s">
         <v>784</v>
       </c>
-      <c r="U76" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T76" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>44</v>
       </c>
@@ -8402,38 +8247,35 @@
       <c r="K77" t="s">
         <v>179</v>
       </c>
-      <c r="L77" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N77" s="16" t="s">
+      <c r="L77" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M77" s="15" t="s">
         <v>783</v>
       </c>
-      <c r="O77" s="16" t="s">
+      <c r="N77" s="15" t="s">
         <v>783</v>
       </c>
-      <c r="P77" s="22" t="s">
+      <c r="O77" s="21" t="s">
         <v>783</v>
       </c>
-      <c r="Q77" s="22" t="s">
+      <c r="P77" s="21" t="s">
         <v>783</v>
       </c>
-      <c r="R77" s="28" t="s">
+      <c r="Q77" s="27" t="s">
         <v>783</v>
       </c>
-      <c r="S77" s="28" t="s">
+      <c r="R77" s="27" t="s">
         <v>783</v>
       </c>
-      <c r="T77" s="36" t="s">
+      <c r="S77" s="35" t="s">
         <v>783</v>
       </c>
-      <c r="U77" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T77" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>46</v>
       </c>
@@ -8467,103 +8309,97 @@
       <c r="K78" t="s">
         <v>179</v>
       </c>
-      <c r="L78" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N78" s="16" t="s">
+      <c r="L78" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M78" s="15" t="s">
         <v>782</v>
       </c>
-      <c r="O78" s="16" t="s">
+      <c r="N78" s="15" t="s">
         <v>782</v>
       </c>
-      <c r="P78" s="22" t="s">
+      <c r="O78" s="21" t="s">
         <v>782</v>
       </c>
-      <c r="Q78" s="22" t="s">
+      <c r="P78" s="21" t="s">
         <v>782</v>
       </c>
-      <c r="R78" s="29" t="s">
+      <c r="Q78" s="28" t="s">
         <v>782</v>
       </c>
-      <c r="S78" s="29" t="s">
+      <c r="R78" s="28" t="s">
         <v>782</v>
       </c>
-      <c r="T78" s="36" t="s">
+      <c r="S78" s="35" t="s">
         <v>782</v>
       </c>
-      <c r="U78" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="5" t="s">
+      <c r="T78" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E79" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="F79" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G79" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H79" s="5" t="s">
+      <c r="H79" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="I79" s="5" t="s">
+      <c r="I79" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="J79" s="5" t="s">
+      <c r="J79" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="K79" s="5" t="s">
+      <c r="K79" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="L79" s="11" t="s">
-        <v>751</v>
-      </c>
-      <c r="M79" s="11" t="s">
-        <v>732</v>
-      </c>
-      <c r="N79" s="17" t="s">
+      <c r="L79" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M79" s="16" t="s">
         <v>781</v>
       </c>
-      <c r="O79" s="17" t="s">
+      <c r="N79" s="16" t="s">
         <v>781</v>
       </c>
-      <c r="P79" s="23" t="s">
+      <c r="O79" s="22" t="s">
         <v>781</v>
       </c>
-      <c r="Q79" s="23" t="s">
+      <c r="P79" s="22" t="s">
         <v>781</v>
       </c>
-      <c r="R79" s="31" t="s">
+      <c r="Q79" s="30" t="s">
         <v>781</v>
       </c>
-      <c r="S79" s="40" t="s">
+      <c r="R79" s="39" t="s">
         <v>848</v>
       </c>
-      <c r="T79" s="36" t="s">
+      <c r="S79" s="35" t="s">
         <v>781</v>
       </c>
-      <c r="U79" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T79" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>518</v>
       </c>
@@ -8597,38 +8433,35 @@
       <c r="K80" t="s">
         <v>179</v>
       </c>
-      <c r="L80" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N80" s="16" t="s">
+      <c r="L80" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M80" s="15" t="s">
         <v>780</v>
       </c>
-      <c r="O80" s="16" t="s">
+      <c r="N80" s="15" t="s">
         <v>780</v>
       </c>
-      <c r="P80" s="22" t="s">
+      <c r="O80" s="21" t="s">
         <v>780</v>
       </c>
-      <c r="Q80" s="22" t="s">
+      <c r="P80" s="21" t="s">
         <v>780</v>
       </c>
-      <c r="R80" s="29" t="s">
+      <c r="Q80" s="28" t="s">
         <v>780</v>
       </c>
-      <c r="S80" s="29" t="s">
+      <c r="R80" s="28" t="s">
         <v>780</v>
       </c>
-      <c r="T80" s="36" t="s">
+      <c r="S80" s="35" t="s">
         <v>780</v>
       </c>
-      <c r="U80" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T80" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>50</v>
       </c>
@@ -8662,38 +8495,35 @@
       <c r="K81" t="s">
         <v>179</v>
       </c>
-      <c r="L81" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M81" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N81" s="16" t="s">
+      <c r="L81" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M81" s="15" t="s">
         <v>809</v>
       </c>
-      <c r="O81" s="16" t="s">
+      <c r="N81" s="15" t="s">
         <v>809</v>
       </c>
-      <c r="P81" s="22" t="s">
+      <c r="O81" s="21" t="s">
         <v>809</v>
       </c>
-      <c r="Q81" s="22" t="s">
+      <c r="P81" s="21" t="s">
         <v>809</v>
       </c>
-      <c r="R81" s="28" t="s">
+      <c r="Q81" s="27" t="s">
         <v>809</v>
       </c>
-      <c r="S81" s="28" t="s">
+      <c r="R81" s="27" t="s">
         <v>809</v>
       </c>
-      <c r="T81" s="36" t="s">
+      <c r="S81" s="35" t="s">
         <v>809</v>
       </c>
-      <c r="U81" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T81" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>52</v>
       </c>
@@ -8727,38 +8557,35 @@
       <c r="K82" t="s">
         <v>179</v>
       </c>
-      <c r="L82" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N82" s="16" t="s">
+      <c r="L82" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M82" s="15" t="s">
         <v>779</v>
       </c>
-      <c r="O82" s="16" t="s">
+      <c r="N82" s="15" t="s">
         <v>779</v>
       </c>
-      <c r="P82" s="22" t="s">
+      <c r="O82" s="21" t="s">
         <v>779</v>
       </c>
-      <c r="Q82" s="22" t="s">
+      <c r="P82" s="21" t="s">
         <v>779</v>
       </c>
-      <c r="R82" s="29" t="s">
+      <c r="Q82" s="28" t="s">
         <v>779</v>
       </c>
-      <c r="S82" s="29" t="s">
+      <c r="R82" s="28" t="s">
         <v>779</v>
       </c>
-      <c r="T82" s="36" t="s">
+      <c r="S82" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="U82" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T82" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>34</v>
       </c>
@@ -8792,38 +8619,35 @@
       <c r="K83" t="s">
         <v>179</v>
       </c>
-      <c r="L83" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N83" s="16" t="s">
+      <c r="L83" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M83" s="15" t="s">
         <v>811</v>
       </c>
-      <c r="O83" s="16" t="s">
+      <c r="N83" s="15" t="s">
         <v>811</v>
       </c>
-      <c r="P83" s="23" t="s">
+      <c r="O83" s="22" t="s">
         <v>812</v>
       </c>
-      <c r="Q83" s="23" t="s">
+      <c r="P83" s="22" t="s">
         <v>812</v>
       </c>
-      <c r="R83" s="31" t="s">
+      <c r="Q83" s="30" t="s">
         <v>810</v>
       </c>
-      <c r="S83" s="40" t="s">
+      <c r="R83" s="39" t="s">
         <v>857</v>
       </c>
-      <c r="T83" s="36" t="s">
+      <c r="S83" s="35" t="s">
         <v>810</v>
       </c>
-      <c r="U83" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T83" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>591</v>
       </c>
@@ -8857,38 +8681,35 @@
       <c r="K84" t="s">
         <v>179</v>
       </c>
-      <c r="L84" s="12" t="s">
+      <c r="L84" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="M84" s="18" t="s">
         <v>768</v>
       </c>
-      <c r="M84" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N84" s="19" t="s">
+      <c r="N84" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O84" s="24" t="s">
         <v>768</v>
       </c>
-      <c r="O84" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P84" s="25" t="s">
+      <c r="P84" s="22" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q84" s="30" t="s">
         <v>768</v>
       </c>
-      <c r="Q84" s="23" t="s">
-        <v>732</v>
-      </c>
-      <c r="R84" s="31" t="s">
+      <c r="R84" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="S84" s="35" t="s">
         <v>768</v>
       </c>
-      <c r="S84" s="29" t="s">
-        <v>732</v>
-      </c>
-      <c r="T84" s="36" t="s">
-        <v>768</v>
-      </c>
-      <c r="U84" s="40" t="s">
+      <c r="T84" s="39" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>561</v>
       </c>
@@ -8923,37 +8744,34 @@
         <v>179</v>
       </c>
       <c r="L85" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="M85" s="15" t="s">
         <v>769</v>
       </c>
-      <c r="M85" s="2" t="s">
+      <c r="N85" s="15" t="s">
         <v>769</v>
       </c>
-      <c r="N85" s="16" t="s">
+      <c r="O85" s="21" t="s">
         <v>769</v>
       </c>
-      <c r="O85" s="16" t="s">
+      <c r="P85" s="21" t="s">
         <v>769</v>
       </c>
-      <c r="P85" s="22" t="s">
+      <c r="Q85" s="28" t="s">
         <v>769</v>
       </c>
-      <c r="Q85" s="22" t="s">
+      <c r="R85" s="28" t="s">
         <v>769</v>
       </c>
-      <c r="R85" s="29" t="s">
+      <c r="S85" s="35" t="s">
         <v>769</v>
       </c>
-      <c r="S85" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="T85" s="36" t="s">
-        <v>769</v>
-      </c>
-      <c r="U85" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T85" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>436</v>
       </c>
@@ -8988,37 +8806,34 @@
         <v>179</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="M86" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N86" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="O86" s="16" t="s">
-        <v>732</v>
-      </c>
-      <c r="P86" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q86" s="22" t="s">
-        <v>732</v>
-      </c>
-      <c r="R86" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="S86" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T86" s="34" t="s">
-        <v>732</v>
-      </c>
-      <c r="U86" s="34" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>937</v>
+      </c>
+      <c r="M86" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="N86" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="O86" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="P86" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q86" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="R86" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S86" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="T86" s="33" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>471</v>
       </c>
@@ -9052,38 +8867,35 @@
       <c r="K87" t="s">
         <v>179</v>
       </c>
-      <c r="L87" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="M87" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N87" s="16" t="s">
+      <c r="L87" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="M87" s="15" t="s">
         <v>787</v>
       </c>
-      <c r="O87" s="16" t="s">
+      <c r="N87" s="15" t="s">
         <v>787</v>
       </c>
-      <c r="P87" s="22" t="s">
+      <c r="O87" s="21" t="s">
         <v>799</v>
       </c>
-      <c r="Q87" s="22" t="s">
+      <c r="P87" s="21" t="s">
         <v>799</v>
       </c>
-      <c r="R87" s="31" t="s">
+      <c r="Q87" s="30" t="s">
         <v>787</v>
       </c>
-      <c r="S87" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="T87" s="36" t="s">
+      <c r="R87" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="S87" s="35" t="s">
         <v>787</v>
       </c>
-      <c r="U87" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T87" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>16</v>
       </c>
@@ -9117,38 +8929,35 @@
       <c r="K88" t="s">
         <v>179</v>
       </c>
-      <c r="L88" s="12" t="s">
+      <c r="L88" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="M88" s="18" t="s">
         <v>751</v>
       </c>
-      <c r="M88" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N88" s="19" t="s">
+      <c r="N88" s="39" t="s">
+        <v>842</v>
+      </c>
+      <c r="O88" s="24" t="s">
         <v>751</v>
       </c>
-      <c r="O88" s="40" t="s">
+      <c r="P88" s="39" t="s">
         <v>842</v>
       </c>
-      <c r="P88" s="25" t="s">
+      <c r="Q88" s="30" t="s">
         <v>751</v>
       </c>
-      <c r="Q88" s="40" t="s">
+      <c r="R88" s="39" t="s">
         <v>842</v>
       </c>
-      <c r="R88" s="31" t="s">
+      <c r="S88" s="35" t="s">
         <v>751</v>
       </c>
-      <c r="S88" s="40" t="s">
+      <c r="T88" s="39" t="s">
         <v>842</v>
       </c>
-      <c r="T88" s="36" t="s">
-        <v>751</v>
-      </c>
-      <c r="U88" s="40" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>20</v>
       </c>
@@ -9182,38 +8991,35 @@
       <c r="K89" t="s">
         <v>179</v>
       </c>
-      <c r="L89" s="12" t="s">
+      <c r="L89" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="M89" s="15" t="s">
         <v>770</v>
       </c>
-      <c r="M89" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N89" s="16" t="s">
+      <c r="N89" s="15" t="s">
         <v>770</v>
       </c>
-      <c r="O89" s="16" t="s">
+      <c r="O89" s="21" t="s">
         <v>770</v>
       </c>
-      <c r="P89" s="22" t="s">
+      <c r="P89" s="21" t="s">
         <v>770</v>
       </c>
-      <c r="Q89" s="22" t="s">
+      <c r="Q89" s="27" t="s">
         <v>770</v>
       </c>
-      <c r="R89" s="28" t="s">
+      <c r="R89" s="27" t="s">
         <v>770</v>
       </c>
-      <c r="S89" s="28" t="s">
+      <c r="S89" s="35" t="s">
         <v>770</v>
       </c>
-      <c r="T89" s="36" t="s">
-        <v>770</v>
-      </c>
-      <c r="U89" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T89" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -9247,103 +9053,97 @@
       <c r="K90" t="s">
         <v>179</v>
       </c>
-      <c r="L90" s="12" t="s">
+      <c r="L90" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="M90" s="15" t="s">
         <v>771</v>
       </c>
-      <c r="M90" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="N90" s="16" t="s">
+      <c r="N90" s="15" t="s">
         <v>771</v>
       </c>
-      <c r="O90" s="16" t="s">
+      <c r="O90" s="21" t="s">
         <v>771</v>
       </c>
-      <c r="P90" s="22" t="s">
+      <c r="P90" s="21" t="s">
         <v>771</v>
       </c>
-      <c r="Q90" s="22" t="s">
+      <c r="Q90" s="27" t="s">
         <v>771</v>
       </c>
-      <c r="R90" s="28" t="s">
+      <c r="R90" s="27" t="s">
         <v>771</v>
       </c>
-      <c r="S90" s="28" t="s">
+      <c r="S90" s="35" t="s">
         <v>771</v>
       </c>
-      <c r="T90" s="36" t="s">
-        <v>771</v>
-      </c>
-      <c r="U90" s="35" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="13" t="s">
+      <c r="T90" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="D91" s="13" t="s">
+      <c r="D91" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="E91" s="14" t="s">
+      <c r="E91" s="13" t="s">
         <v>749</v>
       </c>
-      <c r="F91" s="13" t="s">
+      <c r="F91" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="G91" s="13" t="s">
+      <c r="G91" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="H91" s="13" t="s">
+      <c r="H91" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="I91" s="13" t="s">
+      <c r="I91" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="J91" s="13" t="s">
+      <c r="J91" s="12" t="s">
         <v>602</v>
       </c>
-      <c r="K91" s="13" t="s">
+      <c r="K91" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="L91" s="15" t="s">
-        <v>732</v>
-      </c>
-      <c r="M91" s="15" t="s">
-        <v>732</v>
-      </c>
-      <c r="N91" s="21" t="s">
-        <v>732</v>
-      </c>
-      <c r="O91" s="21" t="s">
-        <v>732</v>
-      </c>
-      <c r="P91" s="27" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q91" s="27" t="s">
-        <v>732</v>
-      </c>
-      <c r="R91" s="32" t="s">
-        <v>732</v>
-      </c>
-      <c r="S91" s="32" t="s">
-        <v>732</v>
-      </c>
-      <c r="T91" s="38" t="s">
-        <v>732</v>
-      </c>
-      <c r="U91" s="38" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="L91" s="14" t="s">
+        <v>937</v>
+      </c>
+      <c r="M91" s="20" t="s">
+        <v>732</v>
+      </c>
+      <c r="N91" s="20" t="s">
+        <v>732</v>
+      </c>
+      <c r="O91" s="26" t="s">
+        <v>732</v>
+      </c>
+      <c r="P91" s="26" t="s">
+        <v>732</v>
+      </c>
+      <c r="Q91" s="31" t="s">
+        <v>732</v>
+      </c>
+      <c r="R91" s="31" t="s">
+        <v>732</v>
+      </c>
+      <c r="S91" s="37" t="s">
+        <v>732</v>
+      </c>
+      <c r="T91" s="37" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>610</v>
       </c>
@@ -9380,35 +9180,32 @@
       <c r="L92" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="M92" s="2" t="s">
+      <c r="M92" s="15" t="s">
         <v>750</v>
       </c>
-      <c r="N92" s="16" t="s">
+      <c r="N92" s="15" t="s">
         <v>750</v>
       </c>
-      <c r="O92" s="16" t="s">
+      <c r="O92" s="21" t="s">
         <v>750</v>
       </c>
-      <c r="P92" s="22" t="s">
+      <c r="P92" s="21" t="s">
         <v>750</v>
       </c>
-      <c r="Q92" s="22" t="s">
+      <c r="Q92" s="27" t="s">
         <v>750</v>
       </c>
-      <c r="R92" s="28" t="s">
+      <c r="R92" s="27" t="s">
         <v>750</v>
       </c>
-      <c r="S92" s="28" t="s">
+      <c r="S92" s="33" t="s">
         <v>750</v>
       </c>
-      <c r="T92" s="34" t="s">
+      <c r="T92" s="33" t="s">
         <v>750</v>
       </c>
-      <c r="U92" s="34" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>603</v>
       </c>
@@ -9445,31 +9242,28 @@
       <c r="L93" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="M93" s="2" t="s">
+      <c r="M93" s="15" t="s">
         <v>750</v>
       </c>
-      <c r="N93" s="16" t="s">
+      <c r="N93" s="15" t="s">
         <v>750</v>
       </c>
-      <c r="O93" s="16" t="s">
+      <c r="O93" s="21" t="s">
         <v>750</v>
       </c>
-      <c r="P93" s="22" t="s">
+      <c r="P93" s="21" t="s">
         <v>750</v>
       </c>
-      <c r="Q93" s="22" t="s">
+      <c r="Q93" s="27" t="s">
         <v>750</v>
       </c>
-      <c r="R93" s="28" t="s">
+      <c r="R93" s="27" t="s">
         <v>750</v>
       </c>
-      <c r="S93" s="28" t="s">
+      <c r="S93" s="33" t="s">
         <v>750</v>
       </c>
-      <c r="T93" s="34" t="s">
-        <v>750</v>
-      </c>
-      <c r="U93" s="34" t="s">
+      <c r="T93" s="33" t="s">
         <v>750</v>
       </c>
     </row>
@@ -9580,257 +9374,257 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="41" t="s">
-        <v>881</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="A1" s="40" t="s">
+        <v>879</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B3" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B4" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B5" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B6" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B7" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B8" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B9" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B10" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B11" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B12" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B13" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B14" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B15" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B16" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B17" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B18" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B19" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A24" s="41" t="s">
-        <v>931</v>
+      <c r="A24" s="40" t="s">
+        <v>929</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
   </sheetData>
@@ -9853,30 +9647,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>860</v>
       </c>
     </row>
@@ -9945,7 +9739,7 @@
       <c r="F6" t="s">
         <v>224</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="10" t="s">
         <v>751</v>
       </c>
     </row>
@@ -10083,7 +9877,7 @@
       <c r="F12" t="s">
         <v>658</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="10" t="s">
         <v>751</v>
       </c>
     </row>
@@ -10215,30 +10009,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>861</v>
       </c>
     </row>
@@ -10261,7 +10055,7 @@
       <c r="F4" t="s">
         <v>175</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>772</v>
       </c>
     </row>
@@ -10284,7 +10078,7 @@
       <c r="F5" t="s">
         <v>691</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>789</v>
       </c>
     </row>
@@ -10307,7 +10101,7 @@
       <c r="F6" t="s">
         <v>701</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="15" t="s">
         <v>752</v>
       </c>
     </row>
@@ -10330,7 +10124,7 @@
       <c r="F7" t="s">
         <v>687</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="15" t="s">
         <v>752</v>
       </c>
     </row>
@@ -10353,7 +10147,7 @@
       <c r="F8" t="s">
         <v>712</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="39" t="s">
         <v>844</v>
       </c>
     </row>
@@ -10376,7 +10170,7 @@
       <c r="F9" t="s">
         <v>688</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="15" t="s">
         <v>753</v>
       </c>
     </row>
@@ -10399,7 +10193,7 @@
       <c r="F10" t="s">
         <v>700</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="15" t="s">
         <v>754</v>
       </c>
     </row>
@@ -10422,7 +10216,7 @@
       <c r="F11" t="s">
         <v>482</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="15" t="s">
         <v>775</v>
       </c>
     </row>
@@ -10445,7 +10239,7 @@
       <c r="F12" t="s">
         <v>240</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>775</v>
       </c>
     </row>
@@ -10468,7 +10262,7 @@
       <c r="F13" t="s">
         <v>235</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="15" t="s">
         <v>775</v>
       </c>
     </row>
@@ -10491,7 +10285,7 @@
       <c r="F14" t="s">
         <v>693</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="15" t="s">
         <v>755</v>
       </c>
     </row>
@@ -10514,7 +10308,7 @@
       <c r="F15" t="s">
         <v>695</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="15" t="s">
         <v>756</v>
       </c>
     </row>
@@ -10537,53 +10331,53 @@
       <c r="F16" t="s">
         <v>694</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="15" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>249</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="16" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>249</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="16" t="s">
         <v>794</v>
       </c>
     </row>
@@ -10606,7 +10400,7 @@
       <c r="F19" t="s">
         <v>245</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="19" t="s">
         <v>795</v>
       </c>
     </row>
@@ -10629,7 +10423,7 @@
       <c r="F20" t="s">
         <v>189</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="39" t="s">
         <v>845</v>
       </c>
     </row>
@@ -10652,7 +10446,7 @@
       <c r="F21" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="15" t="s">
         <v>776</v>
       </c>
     </row>
@@ -10675,7 +10469,7 @@
       <c r="F22" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="15" t="s">
         <v>774</v>
       </c>
     </row>
@@ -10698,7 +10492,7 @@
       <c r="F23" t="s">
         <v>696</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="15" t="s">
         <v>761</v>
       </c>
     </row>
@@ -10721,7 +10515,7 @@
       <c r="F24" t="s">
         <v>692</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="15" t="s">
         <v>762</v>
       </c>
     </row>
@@ -10744,7 +10538,7 @@
       <c r="F25" t="s">
         <v>659</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="15" t="s">
         <v>763</v>
       </c>
     </row>
@@ -10767,7 +10561,7 @@
       <c r="F26" t="s">
         <v>699</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="15" t="s">
         <v>764</v>
       </c>
     </row>
@@ -10790,7 +10584,7 @@
       <c r="F27" t="s">
         <v>658</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="39" t="s">
         <v>842</v>
       </c>
     </row>
@@ -10813,7 +10607,7 @@
       <c r="F28" t="s">
         <v>446</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="15" t="s">
         <v>777</v>
       </c>
     </row>
@@ -10836,7 +10630,7 @@
       <c r="F29" t="s">
         <v>182</v>
       </c>
-      <c r="G29" s="16" t="s">
+      <c r="G29" s="15" t="s">
         <v>765</v>
       </c>
     </row>
@@ -10859,7 +10653,7 @@
       <c r="F30" t="s">
         <v>698</v>
       </c>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="15" t="s">
         <v>766</v>
       </c>
     </row>
@@ -10882,7 +10676,7 @@
       <c r="F31" t="s">
         <v>199</v>
       </c>
-      <c r="G31" s="40" t="s">
+      <c r="G31" s="39" t="s">
         <v>843</v>
       </c>
     </row>
@@ -10905,7 +10699,7 @@
       <c r="F32" t="s">
         <v>660</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="15" t="s">
         <v>778</v>
       </c>
     </row>
@@ -10928,7 +10722,7 @@
       <c r="F33" t="s">
         <v>260</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="15" t="s">
         <v>786</v>
       </c>
     </row>
@@ -10951,7 +10745,7 @@
       <c r="F34" t="s">
         <v>664</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="15" t="s">
         <v>785</v>
       </c>
     </row>
@@ -10974,7 +10768,7 @@
       <c r="F35" t="s">
         <v>269</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="G35" s="15" t="s">
         <v>797</v>
       </c>
     </row>
@@ -10997,7 +10791,7 @@
       <c r="F36" t="s">
         <v>274</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="15" t="s">
         <v>784</v>
       </c>
     </row>
@@ -11020,7 +10814,7 @@
       <c r="F37" t="s">
         <v>665</v>
       </c>
-      <c r="G37" s="16" t="s">
+      <c r="G37" s="15" t="s">
         <v>783</v>
       </c>
     </row>
@@ -11043,30 +10837,30 @@
       <c r="F38" t="s">
         <v>666</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="15" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="16" t="s">
         <v>781</v>
       </c>
     </row>
@@ -11089,7 +10883,7 @@
       <c r="F40" t="s">
         <v>522</v>
       </c>
-      <c r="G40" s="16" t="s">
+      <c r="G40" s="15" t="s">
         <v>780</v>
       </c>
     </row>
@@ -11112,7 +10906,7 @@
       <c r="F41" t="s">
         <v>291</v>
       </c>
-      <c r="G41" s="16" t="s">
+      <c r="G41" s="15" t="s">
         <v>809</v>
       </c>
     </row>
@@ -11135,7 +10929,7 @@
       <c r="F42" t="s">
         <v>668</v>
       </c>
-      <c r="G42" s="16" t="s">
+      <c r="G42" s="15" t="s">
         <v>779</v>
       </c>
     </row>
@@ -11158,7 +10952,7 @@
       <c r="F43" t="s">
         <v>255</v>
       </c>
-      <c r="G43" s="16" t="s">
+      <c r="G43" s="15" t="s">
         <v>811</v>
       </c>
     </row>
@@ -11181,7 +10975,7 @@
       <c r="F44" t="s">
         <v>697</v>
       </c>
-      <c r="G44" s="16" t="s">
+      <c r="G44" s="15" t="s">
         <v>769</v>
       </c>
     </row>
@@ -11204,7 +10998,7 @@
       <c r="F45" t="s">
         <v>475</v>
       </c>
-      <c r="G45" s="16" t="s">
+      <c r="G45" s="15" t="s">
         <v>787</v>
       </c>
     </row>
@@ -11227,7 +11021,7 @@
       <c r="F46" t="s">
         <v>661</v>
       </c>
-      <c r="G46" s="40" t="s">
+      <c r="G46" s="39" t="s">
         <v>842</v>
       </c>
     </row>
@@ -11250,7 +11044,7 @@
       <c r="F47" t="s">
         <v>663</v>
       </c>
-      <c r="G47" s="16" t="s">
+      <c r="G47" s="15" t="s">
         <v>770</v>
       </c>
     </row>
@@ -11273,7 +11067,7 @@
       <c r="F48" t="s">
         <v>662</v>
       </c>
-      <c r="G48" s="16" t="s">
+      <c r="G48" s="15" t="s">
         <v>771</v>
       </c>
     </row>
@@ -11344,30 +11138,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>862</v>
       </c>
     </row>
@@ -11390,7 +11184,7 @@
       <c r="F4" t="s">
         <v>175</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="21" t="s">
         <v>772</v>
       </c>
     </row>
@@ -11413,7 +11207,7 @@
       <c r="F5" t="s">
         <v>691</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="21" t="s">
         <v>789</v>
       </c>
     </row>
@@ -11436,7 +11230,7 @@
       <c r="F6" t="s">
         <v>701</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="21" t="s">
         <v>752</v>
       </c>
     </row>
@@ -11459,7 +11253,7 @@
       <c r="F7" t="s">
         <v>687</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="21" t="s">
         <v>752</v>
       </c>
     </row>
@@ -11482,7 +11276,7 @@
       <c r="F8" t="s">
         <v>712</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="39" t="s">
         <v>844</v>
       </c>
     </row>
@@ -11505,7 +11299,7 @@
       <c r="F9" t="s">
         <v>688</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="21" t="s">
         <v>753</v>
       </c>
     </row>
@@ -11528,7 +11322,7 @@
       <c r="F10" t="s">
         <v>700</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="21" t="s">
         <v>754</v>
       </c>
     </row>
@@ -11551,7 +11345,7 @@
       <c r="F11" t="s">
         <v>482</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="21" t="s">
         <v>732</v>
       </c>
     </row>
@@ -11574,7 +11368,7 @@
       <c r="F12" t="s">
         <v>240</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="21" t="s">
         <v>790</v>
       </c>
     </row>
@@ -11597,7 +11391,7 @@
       <c r="F13" t="s">
         <v>235</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="21" t="s">
         <v>791</v>
       </c>
     </row>
@@ -11620,7 +11414,7 @@
       <c r="F14" t="s">
         <v>693</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="21" t="s">
         <v>755</v>
       </c>
     </row>
@@ -11643,7 +11437,7 @@
       <c r="F15" t="s">
         <v>695</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="21" t="s">
         <v>756</v>
       </c>
     </row>
@@ -11666,53 +11460,53 @@
       <c r="F16" t="s">
         <v>694</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="21" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>249</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="21" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>249</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="21" t="s">
         <v>793</v>
       </c>
     </row>
@@ -11735,7 +11529,7 @@
       <c r="F19" t="s">
         <v>245</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="25" t="s">
         <v>795</v>
       </c>
     </row>
@@ -11758,7 +11552,7 @@
       <c r="F20" t="s">
         <v>189</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="39" t="s">
         <v>845</v>
       </c>
     </row>
@@ -11781,7 +11575,7 @@
       <c r="F21" t="s">
         <v>230</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="21" t="s">
         <v>788</v>
       </c>
     </row>
@@ -11804,7 +11598,7 @@
       <c r="F22" t="s">
         <v>696</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="21" t="s">
         <v>761</v>
       </c>
     </row>
@@ -11827,7 +11621,7 @@
       <c r="F23" t="s">
         <v>692</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="21" t="s">
         <v>762</v>
       </c>
     </row>
@@ -11850,7 +11644,7 @@
       <c r="F24" t="s">
         <v>659</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="21" t="s">
         <v>763</v>
       </c>
     </row>
@@ -11873,7 +11667,7 @@
       <c r="F25" t="s">
         <v>699</v>
       </c>
-      <c r="G25" s="22" t="s">
+      <c r="G25" s="21" t="s">
         <v>764</v>
       </c>
     </row>
@@ -11896,7 +11690,7 @@
       <c r="F26" t="s">
         <v>658</v>
       </c>
-      <c r="G26" s="40" t="s">
+      <c r="G26" s="39" t="s">
         <v>842</v>
       </c>
     </row>
@@ -11919,7 +11713,7 @@
       <c r="F27" t="s">
         <v>446</v>
       </c>
-      <c r="G27" s="22" t="s">
+      <c r="G27" s="21" t="s">
         <v>777</v>
       </c>
     </row>
@@ -11942,7 +11736,7 @@
       <c r="F28" t="s">
         <v>698</v>
       </c>
-      <c r="G28" s="22" t="s">
+      <c r="G28" s="21" t="s">
         <v>766</v>
       </c>
     </row>
@@ -11965,7 +11759,7 @@
       <c r="F29" t="s">
         <v>199</v>
       </c>
-      <c r="G29" s="40" t="s">
+      <c r="G29" s="39" t="s">
         <v>843</v>
       </c>
     </row>
@@ -11988,7 +11782,7 @@
       <c r="F30" t="s">
         <v>660</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="21" t="s">
         <v>778</v>
       </c>
     </row>
@@ -12011,7 +11805,7 @@
       <c r="F31" t="s">
         <v>260</v>
       </c>
-      <c r="G31" s="22" t="s">
+      <c r="G31" s="21" t="s">
         <v>786</v>
       </c>
     </row>
@@ -12034,7 +11828,7 @@
       <c r="F32" t="s">
         <v>664</v>
       </c>
-      <c r="G32" s="22" t="s">
+      <c r="G32" s="21" t="s">
         <v>785</v>
       </c>
     </row>
@@ -12057,7 +11851,7 @@
       <c r="F33" t="s">
         <v>269</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="21" t="s">
         <v>798</v>
       </c>
     </row>
@@ -12080,7 +11874,7 @@
       <c r="F34" t="s">
         <v>274</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="21" t="s">
         <v>784</v>
       </c>
     </row>
@@ -12103,7 +11897,7 @@
       <c r="F35" t="s">
         <v>665</v>
       </c>
-      <c r="G35" s="22" t="s">
+      <c r="G35" s="21" t="s">
         <v>783</v>
       </c>
     </row>
@@ -12126,30 +11920,30 @@
       <c r="F36" t="s">
         <v>666</v>
       </c>
-      <c r="G36" s="22" t="s">
+      <c r="G36" s="21" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="G37" s="23" t="s">
+      <c r="G37" s="22" t="s">
         <v>781</v>
       </c>
     </row>
@@ -12172,7 +11966,7 @@
       <c r="F38" t="s">
         <v>522</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="21" t="s">
         <v>780</v>
       </c>
     </row>
@@ -12195,7 +11989,7 @@
       <c r="F39" t="s">
         <v>291</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="21" t="s">
         <v>809</v>
       </c>
     </row>
@@ -12218,7 +12012,7 @@
       <c r="F40" t="s">
         <v>668</v>
       </c>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="21" t="s">
         <v>779</v>
       </c>
     </row>
@@ -12241,7 +12035,7 @@
       <c r="F41" t="s">
         <v>255</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="G41" s="22" t="s">
         <v>812</v>
       </c>
     </row>
@@ -12264,7 +12058,7 @@
       <c r="F42" t="s">
         <v>697</v>
       </c>
-      <c r="G42" s="22" t="s">
+      <c r="G42" s="21" t="s">
         <v>769</v>
       </c>
     </row>
@@ -12287,7 +12081,7 @@
       <c r="F43" t="s">
         <v>475</v>
       </c>
-      <c r="G43" s="22" t="s">
+      <c r="G43" s="21" t="s">
         <v>799</v>
       </c>
     </row>
@@ -12310,7 +12104,7 @@
       <c r="F44" t="s">
         <v>661</v>
       </c>
-      <c r="G44" s="40" t="s">
+      <c r="G44" s="39" t="s">
         <v>842</v>
       </c>
     </row>
@@ -12333,7 +12127,7 @@
       <c r="F45" t="s">
         <v>663</v>
       </c>
-      <c r="G45" s="22" t="s">
+      <c r="G45" s="21" t="s">
         <v>770</v>
       </c>
     </row>
@@ -12356,7 +12150,7 @@
       <c r="F46" t="s">
         <v>662</v>
       </c>
-      <c r="G46" s="22" t="s">
+      <c r="G46" s="21" t="s">
         <v>771</v>
       </c>
     </row>
@@ -12425,30 +12219,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>863</v>
       </c>
     </row>
@@ -12471,7 +12265,7 @@
       <c r="F4" t="s">
         <v>175</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>772</v>
       </c>
     </row>
@@ -12494,7 +12288,7 @@
       <c r="F5" t="s">
         <v>691</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="27" t="s">
         <v>789</v>
       </c>
     </row>
@@ -12517,7 +12311,7 @@
       <c r="F6" t="s">
         <v>496</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="27" t="s">
         <v>800</v>
       </c>
     </row>
@@ -12540,7 +12334,7 @@
       <c r="F7" t="s">
         <v>684</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="28" t="s">
         <v>801</v>
       </c>
     </row>
@@ -12563,7 +12357,7 @@
       <c r="F8" t="s">
         <v>390</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="28" t="s">
         <v>802</v>
       </c>
     </row>
@@ -12586,7 +12380,7 @@
       <c r="F9" t="s">
         <v>390</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="28" t="s">
         <v>803</v>
       </c>
     </row>
@@ -12603,36 +12397,36 @@
       <c r="D10" t="s">
         <v>398</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>159</v>
       </c>
       <c r="F10" t="s">
         <v>399</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="27" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="39" t="s">
         <v>846</v>
       </c>
     </row>
@@ -12655,7 +12449,7 @@
       <c r="F12" t="s">
         <v>711</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="28" t="s">
         <v>806</v>
       </c>
     </row>
@@ -12678,7 +12472,7 @@
       <c r="F13" t="s">
         <v>683</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="28" t="s">
         <v>807</v>
       </c>
     </row>
@@ -12701,7 +12495,7 @@
       <c r="F14" t="s">
         <v>712</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="39" t="s">
         <v>844</v>
       </c>
     </row>
@@ -12718,13 +12512,13 @@
       <c r="D15" t="s">
         <v>403</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>160</v>
       </c>
       <c r="F15" t="s">
         <v>686</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="39" t="s">
         <v>847</v>
       </c>
     </row>
@@ -12747,7 +12541,7 @@
       <c r="F16" t="s">
         <v>688</v>
       </c>
-      <c r="G16" s="28" t="s">
+      <c r="G16" s="27" t="s">
         <v>753</v>
       </c>
     </row>
@@ -12770,7 +12564,7 @@
       <c r="F17" t="s">
         <v>693</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="G17" s="27" t="s">
         <v>755</v>
       </c>
     </row>
@@ -12793,7 +12587,7 @@
       <c r="F18" t="s">
         <v>695</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="27" t="s">
         <v>756</v>
       </c>
     </row>
@@ -12816,7 +12610,7 @@
       <c r="F19" t="s">
         <v>694</v>
       </c>
-      <c r="G19" s="28" t="s">
+      <c r="G19" s="27" t="s">
         <v>757</v>
       </c>
     </row>
@@ -12839,7 +12633,7 @@
       <c r="F20" t="s">
         <v>659</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="G20" s="27" t="s">
         <v>763</v>
       </c>
     </row>
@@ -12862,7 +12656,7 @@
       <c r="F21" t="s">
         <v>699</v>
       </c>
-      <c r="G21" s="28" t="s">
+      <c r="G21" s="27" t="s">
         <v>764</v>
       </c>
     </row>
@@ -12885,7 +12679,7 @@
       <c r="F22" t="s">
         <v>658</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="39" t="s">
         <v>842</v>
       </c>
     </row>
@@ -12908,7 +12702,7 @@
       <c r="F23" t="s">
         <v>446</v>
       </c>
-      <c r="G23" s="28" t="s">
+      <c r="G23" s="27" t="s">
         <v>777</v>
       </c>
     </row>
@@ -12931,7 +12725,7 @@
       <c r="F24" t="s">
         <v>698</v>
       </c>
-      <c r="G24" s="28" t="s">
+      <c r="G24" s="27" t="s">
         <v>766</v>
       </c>
     </row>
@@ -12954,7 +12748,7 @@
       <c r="F25" t="s">
         <v>199</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="39" t="s">
         <v>843</v>
       </c>
     </row>
@@ -12977,7 +12771,7 @@
       <c r="F26" t="s">
         <v>660</v>
       </c>
-      <c r="G26" s="28" t="s">
+      <c r="G26" s="27" t="s">
         <v>778</v>
       </c>
     </row>
@@ -13000,7 +12794,7 @@
       <c r="F27" t="s">
         <v>260</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="39" t="s">
         <v>855</v>
       </c>
     </row>
@@ -13023,7 +12817,7 @@
       <c r="F28" t="s">
         <v>664</v>
       </c>
-      <c r="G28" s="28" t="s">
+      <c r="G28" s="27" t="s">
         <v>785</v>
       </c>
     </row>
@@ -13046,7 +12840,7 @@
       <c r="F29" t="s">
         <v>269</v>
       </c>
-      <c r="G29" s="40" t="s">
+      <c r="G29" s="39" t="s">
         <v>864</v>
       </c>
     </row>
@@ -13069,7 +12863,7 @@
       <c r="F30" t="s">
         <v>274</v>
       </c>
-      <c r="G30" s="29" t="s">
+      <c r="G30" s="28" t="s">
         <v>784</v>
       </c>
     </row>
@@ -13092,7 +12886,7 @@
       <c r="F31" t="s">
         <v>665</v>
       </c>
-      <c r="G31" s="28" t="s">
+      <c r="G31" s="27" t="s">
         <v>783</v>
       </c>
     </row>
@@ -13115,30 +12909,30 @@
       <c r="F32" t="s">
         <v>666</v>
       </c>
-      <c r="G32" s="29" t="s">
+      <c r="G32" s="28" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="G33" s="40" t="s">
+      <c r="G33" s="39" t="s">
         <v>848</v>
       </c>
     </row>
@@ -13161,7 +12955,7 @@
       <c r="F34" t="s">
         <v>522</v>
       </c>
-      <c r="G34" s="29" t="s">
+      <c r="G34" s="28" t="s">
         <v>780</v>
       </c>
     </row>
@@ -13184,7 +12978,7 @@
       <c r="F35" t="s">
         <v>291</v>
       </c>
-      <c r="G35" s="28" t="s">
+      <c r="G35" s="27" t="s">
         <v>809</v>
       </c>
     </row>
@@ -13207,7 +13001,7 @@
       <c r="F36" t="s">
         <v>668</v>
       </c>
-      <c r="G36" s="29" t="s">
+      <c r="G36" s="28" t="s">
         <v>779</v>
       </c>
     </row>
@@ -13230,7 +13024,7 @@
       <c r="F37" t="s">
         <v>255</v>
       </c>
-      <c r="G37" s="40" t="s">
+      <c r="G37" s="39" t="s">
         <v>857</v>
       </c>
     </row>
@@ -13253,7 +13047,7 @@
       <c r="F38" t="s">
         <v>697</v>
       </c>
-      <c r="G38" s="29" t="s">
+      <c r="G38" s="28" t="s">
         <v>769</v>
       </c>
     </row>
@@ -13276,7 +13070,7 @@
       <c r="F39" t="s">
         <v>661</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G39" s="39" t="s">
         <v>842</v>
       </c>
     </row>
@@ -13299,7 +13093,7 @@
       <c r="F40" t="s">
         <v>663</v>
       </c>
-      <c r="G40" s="28" t="s">
+      <c r="G40" s="27" t="s">
         <v>770</v>
       </c>
     </row>
@@ -13322,7 +13116,7 @@
       <c r="F41" t="s">
         <v>662</v>
       </c>
-      <c r="G41" s="28" t="s">
+      <c r="G41" s="27" t="s">
         <v>771</v>
       </c>
     </row>
@@ -13374,7 +13168,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1CB6B1-EAED-4E89-95DD-0B4543F0E2B7}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="7.3125" bestFit="1" customWidth="1"/>
@@ -13387,30 +13181,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>865</v>
       </c>
     </row>
@@ -13433,7 +13227,7 @@
       <c r="F4" t="s">
         <v>175</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="33" t="s">
         <v>772</v>
       </c>
     </row>
@@ -13456,7 +13250,7 @@
       <c r="F5" t="s">
         <v>691</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="33" t="s">
         <v>789</v>
       </c>
     </row>
@@ -13479,7 +13273,7 @@
       <c r="F6" t="s">
         <v>689</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="34" t="s">
         <v>813</v>
       </c>
     </row>
@@ -13502,7 +13296,7 @@
       <c r="F7" t="s">
         <v>489</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="39" t="s">
         <v>849</v>
       </c>
     </row>
@@ -13525,7 +13319,7 @@
       <c r="F8" t="s">
         <v>361</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="34" t="s">
         <v>814</v>
       </c>
     </row>
@@ -13548,7 +13342,7 @@
       <c r="F9" t="s">
         <v>679</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="34" t="s">
         <v>815</v>
       </c>
     </row>
@@ -13571,7 +13365,7 @@
       <c r="F10" t="s">
         <v>680</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="34" t="s">
         <v>816</v>
       </c>
     </row>
@@ -13594,7 +13388,7 @@
       <c r="F11" t="s">
         <v>681</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G11" s="34" t="s">
         <v>817</v>
       </c>
     </row>
@@ -13617,7 +13411,7 @@
       <c r="F12" t="s">
         <v>678</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="34" t="s">
         <v>818</v>
       </c>
     </row>
@@ -13640,30 +13434,30 @@
       <c r="F13" t="s">
         <v>669</v>
       </c>
-      <c r="G13" s="35" t="s">
+      <c r="G13" s="34" t="s">
         <v>819</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="G14" s="35" t="s">
+      <c r="G14" s="34" t="s">
         <v>820</v>
       </c>
     </row>
@@ -13686,7 +13480,7 @@
       <c r="F15" t="s">
         <v>503</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="34" t="s">
         <v>831</v>
       </c>
     </row>
@@ -13709,7 +13503,7 @@
       <c r="F16" t="s">
         <v>673</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="34" t="s">
         <v>830</v>
       </c>
     </row>
@@ -13732,7 +13526,7 @@
       <c r="F17" t="s">
         <v>674</v>
       </c>
-      <c r="G17" s="34" t="s">
+      <c r="G17" s="33" t="s">
         <v>821</v>
       </c>
     </row>
@@ -13755,7 +13549,7 @@
       <c r="F18" t="s">
         <v>433</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="34" t="s">
         <v>829</v>
       </c>
     </row>
@@ -13778,7 +13572,7 @@
       <c r="F19" t="s">
         <v>675</v>
       </c>
-      <c r="G19" s="35" t="s">
+      <c r="G19" s="34" t="s">
         <v>828</v>
       </c>
     </row>
@@ -13801,30 +13595,30 @@
       <c r="F20" t="s">
         <v>344</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="34" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>348</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="39" t="s">
         <v>851</v>
       </c>
     </row>
@@ -13847,7 +13641,7 @@
       <c r="F22" t="s">
         <v>677</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="34" t="s">
         <v>823</v>
       </c>
     </row>
@@ -13870,7 +13664,7 @@
       <c r="F23" t="s">
         <v>672</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="34" t="s">
         <v>824</v>
       </c>
     </row>
@@ -13893,7 +13687,7 @@
       <c r="F24" t="s">
         <v>670</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G24" s="34" t="s">
         <v>825</v>
       </c>
     </row>
@@ -13916,7 +13710,7 @@
       <c r="F25" t="s">
         <v>426</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="34" t="s">
         <v>827</v>
       </c>
     </row>
@@ -13939,7 +13733,7 @@
       <c r="F26" t="s">
         <v>671</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="34" t="s">
         <v>826</v>
       </c>
     </row>
@@ -13962,7 +13756,7 @@
       <c r="F27" t="s">
         <v>682</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="34" t="s">
         <v>832</v>
       </c>
     </row>
@@ -13985,7 +13779,7 @@
       <c r="F28" t="s">
         <v>710</v>
       </c>
-      <c r="G28" s="35" t="s">
+      <c r="G28" s="34" t="s">
         <v>833</v>
       </c>
     </row>
@@ -14008,7 +13802,7 @@
       <c r="F29" t="s">
         <v>708</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="34" t="s">
         <v>834</v>
       </c>
     </row>
@@ -14031,7 +13825,7 @@
       <c r="F30" t="s">
         <v>709</v>
       </c>
-      <c r="G30" s="35" t="s">
+      <c r="G30" s="34" t="s">
         <v>835</v>
       </c>
     </row>
@@ -14054,7 +13848,7 @@
       <c r="F31" t="s">
         <v>707</v>
       </c>
-      <c r="G31" s="35" t="s">
+      <c r="G31" s="34" t="s">
         <v>836</v>
       </c>
     </row>
@@ -14077,7 +13871,7 @@
       <c r="F32" t="s">
         <v>390</v>
       </c>
-      <c r="G32" s="40" t="s">
+      <c r="G32" s="39" t="s">
         <v>852</v>
       </c>
     </row>
@@ -14100,7 +13894,7 @@
       <c r="F33" t="s">
         <v>305</v>
       </c>
-      <c r="G33" s="35" t="s">
+      <c r="G33" s="34" t="s">
         <v>837</v>
       </c>
     </row>
@@ -14123,7 +13917,7 @@
       <c r="F34" t="s">
         <v>300</v>
       </c>
-      <c r="G34" s="40" t="s">
+      <c r="G34" s="39" t="s">
         <v>853</v>
       </c>
     </row>
@@ -14146,7 +13940,7 @@
       <c r="F35" t="s">
         <v>693</v>
       </c>
-      <c r="G35" s="34" t="s">
+      <c r="G35" s="33" t="s">
         <v>755</v>
       </c>
     </row>
@@ -14169,7 +13963,7 @@
       <c r="F36" t="s">
         <v>695</v>
       </c>
-      <c r="G36" s="34" t="s">
+      <c r="G36" s="33" t="s">
         <v>756</v>
       </c>
     </row>
@@ -14192,7 +13986,7 @@
       <c r="F37" t="s">
         <v>694</v>
       </c>
-      <c r="G37" s="34" t="s">
+      <c r="G37" s="33" t="s">
         <v>757</v>
       </c>
     </row>
@@ -14215,7 +14009,7 @@
       <c r="F38" t="s">
         <v>189</v>
       </c>
-      <c r="G38" s="40" t="s">
+      <c r="G38" s="39" t="s">
         <v>858</v>
       </c>
     </row>
@@ -14238,7 +14032,7 @@
       <c r="F39" t="s">
         <v>658</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G39" s="39" t="s">
         <v>842</v>
       </c>
     </row>
@@ -14261,7 +14055,7 @@
       <c r="F40" t="s">
         <v>446</v>
       </c>
-      <c r="G40" s="34" t="s">
+      <c r="G40" s="33" t="s">
         <v>777</v>
       </c>
     </row>
@@ -14284,7 +14078,7 @@
       <c r="F41" t="s">
         <v>702</v>
       </c>
-      <c r="G41" s="40" t="s">
+      <c r="G41" s="39" t="s">
         <v>859</v>
       </c>
     </row>
@@ -14307,7 +14101,7 @@
       <c r="F42" t="s">
         <v>661</v>
       </c>
-      <c r="G42" s="40" t="s">
+      <c r="G42" s="39" t="s">
         <v>842</v>
       </c>
     </row>
